--- a/data/ams_weekly_data/Audio_Array/business_report_week28.xlsx
+++ b/data/ams_weekly_data/Audio_Array/business_report_week28.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,121 +413,121 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W160"/>
+  <dimension ref="A1:W161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>(Parent) ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>(Child) ASIN</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Sessions - Total</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Sessions - Total - B2B</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Session Percentage - Total</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Session Percentage - Total - B2B</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Page Views - Total</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Page Views - Total - B2B</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Page Views Percentage - Total</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Page Views Percentage - Total - B2B</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Featured Offer Percentage</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Featured Offer Percentage - B2B</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>units_ordered</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Units Ordered - B2B</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Unit Session Percentage</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Unit Session Percentage - B2B</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>ordered_product_sales</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Ordered Product Sales - B2B</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Total Order Items</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Total Order Items - B2B</t>
         </is>
@@ -602,7 +590,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -614,7 +602,7 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>418102.9</v>
+        <v>460069.93</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -764,7 +752,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -776,7 +764,7 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>34057.92</v>
+        <v>37429.11</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -845,7 +833,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -857,7 +845,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>7964.4</v>
+        <v>11946.6</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1084,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1096,7 +1084,7 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>46923.75</v>
+        <v>52261.89</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1323,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1335,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>9705.959999999999</v>
+        <v>14025.47</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1404,7 +1392,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1416,7 +1404,7 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>5294.07</v>
+        <v>7115.26</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1485,7 +1473,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1497,7 +1485,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>5966.96</v>
+        <v>6833.9</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1647,7 +1635,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -1659,7 +1647,7 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>8471.200000000001</v>
+        <v>12706.8</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -1728,7 +1716,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -1740,7 +1728,7 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>42395.73</v>
+        <v>45784.71</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -1809,7 +1797,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -1821,7 +1809,7 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>27361.9</v>
+        <v>29479.7</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -1890,7 +1878,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -1902,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>23322.04</v>
+        <v>26072.04</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -2237,31 +2225,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FBA76862</t>
+          <t>FBA76728</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AM-C28</t>
+          <t>AM-C25</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0BPLWW72Y</t>
+          <t>B0BLNCP74M</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>B0BPLWW72Y</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>AM-C28</t>
-        </is>
-      </c>
+          <t>B0BLNCP74M</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
-        <v>1149</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -2273,7 +2257,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>1561</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2291,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -2303,7 +2287,7 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>54740.76</v>
+        <v>1863.56</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -2318,31 +2302,31 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FBA76864</t>
+          <t>FBA76862</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AI-04 Red</t>
+          <t>AM-C28</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0BPLWW72Y</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0BPLWW72Y</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AI-04 Red</t>
+          <t>AM-C28</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>10416</v>
+        <v>1149</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -2354,7 +2338,7 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>14520</v>
+        <v>1561</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2372,7 +2356,7 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>128</v>
+        <v>44</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -2384,7 +2368,7 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>524966.73</v>
+        <v>59009.4</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2399,31 +2383,31 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FBA76863</t>
+          <t>FBA76864</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AI-03</t>
+          <t>AI-04 Red</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0BPM2T7BQ</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>B0BPM2T7BQ</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AI-03</t>
+          <t>AI-04 Red</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1354</v>
+        <v>10416</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -2435,7 +2419,7 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>1793</v>
+        <v>14520</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -2453,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1</v>
+        <v>148</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2465,7 +2449,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>3219.49</v>
+        <v>609695.53</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -2480,27 +2464,31 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FBA77010</t>
+          <t>FBA76863</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AI-04 Black</t>
+          <t>AI-03</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0BPMBMN3S</t>
+          <t>B0BPM2T7BQ</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>B0BPMBMN3S</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
+          <t>B0BPM2T7BQ</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AI-03</t>
+        </is>
+      </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1354</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -2512,7 +2500,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1793</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -2530,7 +2518,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -2542,7 +2530,7 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>9997.450000000001</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -2557,31 +2545,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FBA77011</t>
+          <t>FBA77010</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AM-C29</t>
+          <t>AI-04 Black</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0BPMN89NG</t>
+          <t>B0BPMBMN3S</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>B0BPMN89NG</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>AM-C29</t>
-        </is>
-      </c>
+          <t>B0BPMBMN3S</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -2593,7 +2577,7 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -2611,7 +2595,7 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -2623,7 +2607,7 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>1482.2</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2638,31 +2622,31 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FBA76597</t>
+          <t>FBA77011</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AA-06</t>
+          <t>AM-C29</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0BQ7H7418</t>
+          <t>B0BPMN89NG</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>B0BQ7H7418</t>
+          <t>B0BPMN89NG</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AA-06</t>
+          <t>AM-C29</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>301</v>
+        <v>85</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -2674,7 +2658,7 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>386</v>
+        <v>127</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -2692,7 +2676,7 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -2704,7 +2688,7 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>11446.59</v>
+        <v>1482.2</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -2719,31 +2703,31 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FBA78204</t>
+          <t>FBA76597</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AM-C31</t>
+          <t>AA-06</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B0C4YT43Z3</t>
+          <t>B0BQ7H7418</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>B0C4YT43Z3</t>
+          <t>B0BQ7H7418</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AM-C31</t>
+          <t>AA-06</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>11</v>
+        <v>301</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -2755,7 +2739,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>13</v>
+        <v>386</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -2773,7 +2757,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -2785,7 +2769,7 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>12547.44</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -2800,31 +2784,31 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FBA78203</t>
+          <t>FBA78204</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>AM-C30</t>
+          <t>AM-C31</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B0C4YTNJG7</t>
+          <t>B0C4YT43Z3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>B0C4YTNJG7</t>
+          <t>B0C4YT43Z3</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AM-C30</t>
+          <t>AM-C31</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -2836,7 +2820,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -2881,31 +2865,31 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>FBA78205</t>
+          <t>FBA78203</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AM-C32</t>
+          <t>AM-C30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B0C539RBGL</t>
+          <t>B0C4YTNJG7</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>B0C539RBGL</t>
+          <t>B0C4YTNJG7</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AM-C32</t>
+          <t>AM-C30</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -2917,7 +2901,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -2962,31 +2946,31 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>FBA78420</t>
+          <t>FBA78205</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AM-C33</t>
+          <t>AM-C32</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0C5957W3P</t>
+          <t>B0C539RBGL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>B0C5957W3P</t>
+          <t>B0C539RBGL</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AM-C33</t>
+          <t>AM-C32</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -2998,7 +2982,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -3043,31 +3027,31 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FBA78423</t>
+          <t>FBA78420</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AM-C36</t>
+          <t>AM-C33</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0C598Q6PT</t>
+          <t>B0C5957W3P</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>B0C598Q6PT</t>
+          <t>B0C5957W3P</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AM-C36</t>
+          <t>AM-C33</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -3079,7 +3063,7 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -3124,31 +3108,31 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>FBA78925</t>
+          <t>FBA78423</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>AM-C11X</t>
+          <t>AM-C36</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0CBC7QMNV</t>
+          <t>B0C598Q6PT</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>B0CBC7QMNV</t>
+          <t>B0C598Q6PT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AM-C11X</t>
+          <t>AM-C36</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>207</v>
+        <v>6</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -3160,7 +3144,7 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>264</v>
+        <v>6</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -3205,31 +3189,31 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>FBA78960</t>
+          <t>FBA78925</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>AM-C39</t>
+          <t>AM-C11X</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0CBCB82MT</t>
+          <t>B0CBC7QMNV</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>B0CBCB82MT</t>
+          <t>B0CBC7QMNV</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AM-C39</t>
+          <t>AM-C11X</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>786</v>
+        <v>207</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -3241,7 +3225,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>1116</v>
+        <v>264</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -3259,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -3271,7 +3255,7 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>10755.9</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -3286,31 +3270,31 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>FBA78973</t>
+          <t>FBA78960</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AA-19</t>
+          <t>AM-C39</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0CF5R3V95</t>
+          <t>B0CBCB82MT</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>B0CF5R3V95</t>
+          <t>B0CBCB82MT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AA-19</t>
+          <t>AM-C39</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>926</v>
+        <v>786</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -3322,7 +3306,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>1308</v>
+        <v>1116</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -3340,7 +3324,7 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -3352,7 +3336,7 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>100531.4</v>
+        <v>12110.98</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -3367,31 +3351,31 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FBA78974</t>
+          <t>FBA78973</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AA-20</t>
+          <t>AA-19</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0CF5RRTDJ</t>
+          <t>B0CF5R3V95</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>B0CF5RRTDJ</t>
+          <t>B0CF5R3V95</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AA-20</t>
+          <t>AA-19</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>116</v>
+        <v>926</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -3403,7 +3387,7 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>171</v>
+        <v>1308</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -3421,7 +3405,7 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -3433,7 +3417,7 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>8470.35</v>
+        <v>114053.42</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -3448,31 +3432,31 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>FBA78976</t>
+          <t>FBA78974</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AA-22</t>
+          <t>AA-20</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0CF5SHL15</t>
+          <t>B0CF5RRTDJ</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>B0CF5SHL15</t>
+          <t>B0CF5RRTDJ</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AA-22</t>
+          <t>AA-20</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>786</v>
+        <v>116</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -3484,7 +3468,7 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>944</v>
+        <v>171</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -3502,7 +3486,7 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -3514,7 +3498,7 @@
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>30337.27</v>
+        <v>8470.35</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -3529,31 +3513,31 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FBA78975</t>
+          <t>FBA78976</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AA-21</t>
+          <t>AA-22</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0CF5TCQKL</t>
+          <t>B0CF5SHL15</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>B0CF5TCQKL</t>
+          <t>B0CF5SHL15</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AA-21</t>
+          <t>AA-22</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2086</v>
+        <v>786</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -3565,7 +3549,7 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>2924</v>
+        <v>944</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -3583,7 +3567,7 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -3595,7 +3579,7 @@
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>125435.88</v>
+        <v>27202.52</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -3610,31 +3594,31 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>FBA79009</t>
+          <t>FBA78975</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AM-C41</t>
+          <t>AA-21</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B0CH4PMR8K</t>
+          <t>B0CF5TCQKL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>B0CH4PMR8K</t>
+          <t>B0CF5TCQKL</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AM-C41</t>
+          <t>AA-21</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>262</v>
+        <v>2086</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -3646,7 +3630,7 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>387</v>
+        <v>2924</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -3664,7 +3648,7 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -3676,7 +3660,7 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>5316.11</v>
+        <v>152059.59</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -3691,31 +3675,31 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FBA79016</t>
+          <t>FBA79009</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AM-C3a</t>
+          <t>AM-C41</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B0CH4R1V6S</t>
+          <t>B0CH4PMR8K</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>B0CH4R1V6S</t>
+          <t>B0CH4PMR8K</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AM-C3a</t>
+          <t>AM-C41</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>168</v>
+        <v>262</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -3727,7 +3711,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>243</v>
+        <v>387</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -3745,7 +3729,7 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -3757,7 +3741,7 @@
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>634.75</v>
+        <v>6671.190000000001</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -3772,31 +3756,31 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FBA79011</t>
+          <t>FBA79016</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>AM-C43</t>
+          <t>AM-C3a</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B0CH4RNWJX</t>
+          <t>B0CH4R1V6S</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>B0CH4RNWJX</t>
+          <t>B0CH4R1V6S</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AM-C43</t>
+          <t>AM-C3a</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1176</v>
+        <v>168</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -3808,7 +3792,7 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>1763</v>
+        <v>243</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -3826,7 +3810,7 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -3838,7 +3822,7 @@
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>41913.6</v>
+        <v>1311.87</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -3853,31 +3837,31 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FBA79008</t>
+          <t>FBA79011</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>AI-06</t>
+          <t>AM-C43</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B0CH4RT4P8</t>
+          <t>B0CH4RNWJX</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>B0CH4RT4P8</t>
+          <t>B0CH4RNWJX</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AI-06</t>
+          <t>AM-C43</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>621</v>
+        <v>1176</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -3889,7 +3873,7 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>880</v>
+        <v>1763</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -3907,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -3919,7 +3903,7 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>4330.7</v>
+        <v>50384.8</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
@@ -3934,31 +3918,31 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FBA79010</t>
+          <t>FBA79008</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AM-C42</t>
+          <t>AI-06</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>B0CH4T2BJD</t>
+          <t>B0CH4RT4P8</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>B0CH4T2BJD</t>
+          <t>B0CH4RT4P8</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AM-C42</t>
+          <t>AI-06</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>171</v>
+        <v>621</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -3970,7 +3954,7 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>245</v>
+        <v>880</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -3988,7 +3972,7 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -4000,7 +3984,7 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>1948.31</v>
+        <v>4330.7</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -4015,31 +3999,31 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>FBA77171</t>
+          <t>FBA79010</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>AC-6XL</t>
+          <t>AM-C42</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>B0CH4VCD6R</t>
+          <t>B0CH4T2BJD</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>B0CH4VCD6R</t>
+          <t>B0CH4T2BJD</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AC-6XL</t>
+          <t>AM-C42</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>664</v>
+        <v>171</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -4051,7 +4035,7 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>1014</v>
+        <v>245</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -4069,7 +4053,7 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -4081,7 +4065,7 @@
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>20974.57</v>
+        <v>1948.31</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
@@ -4096,31 +4080,31 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FBA79064</t>
+          <t>FBA77171</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>AA-25</t>
+          <t>AC-6XL</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B0CJR76Y7G</t>
+          <t>B0CH4VCD6R</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>B0CJR76Y7G</t>
+          <t>B0CH4VCD6R</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AA-25</t>
+          <t>AC-6XL</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>433</v>
+        <v>664</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -4132,7 +4116,7 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>641</v>
+        <v>1014</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -4150,7 +4134,7 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -4162,7 +4146,7 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>6305.93</v>
+        <v>23300.85</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -4177,31 +4161,31 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FBA79005</t>
+          <t>FBA79064</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AM-W45</t>
+          <t>AA-25</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0CJR76Y7G</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0CJR76Y7G</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AM-W45</t>
+          <t>AA-25</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1164</v>
+        <v>433</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -4213,7 +4197,7 @@
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>1613</v>
+        <v>641</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -4231,7 +4215,7 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -4243,7 +4227,7 @@
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>180021.79</v>
+        <v>9183.889999999999</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
@@ -4258,31 +4242,31 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FBA79103</t>
+          <t>FBA79005</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AI-10</t>
+          <t>AM-W45</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>B0CM6NTWBP</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>B0CM6NTWBP</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AI-10</t>
+          <t>AM-W45</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1219</v>
+        <v>1164</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -4294,7 +4278,7 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>1880</v>
+        <v>1613</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -4312,7 +4296,7 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -4324,7 +4308,7 @@
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>53939.84</v>
+        <v>180021.79</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
@@ -4339,31 +4323,31 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FBA79104</t>
+          <t>FBA79103</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AI-11</t>
+          <t>AI-10</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>B0CM6NVLT9</t>
+          <t>B0CM6NTWBP</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>B0CM6NVLT9</t>
+          <t>B0CM6NTWBP</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AI-11</t>
+          <t>AI-10</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1589</v>
+        <v>1219</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -4375,7 +4359,7 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>2399</v>
+        <v>1880</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -4393,7 +4377,7 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -4405,7 +4389,7 @@
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>27932.14</v>
+        <v>56566.11</v>
       </c>
       <c r="U49" t="n">
         <v>0</v>
@@ -4420,31 +4404,31 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>FBA79105</t>
+          <t>FBA79104</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AI-12</t>
+          <t>AI-11</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>B0CM6WH4ZT</t>
+          <t>B0CM6NVLT9</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>B0CM6WH4ZT</t>
+          <t>B0CM6NVLT9</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AI-12</t>
+          <t>AI-11</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>934</v>
+        <v>1589</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -4456,7 +4440,7 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>1264</v>
+        <v>2399</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -4474,7 +4458,7 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -4486,7 +4470,7 @@
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>9357.629999999999</v>
+        <v>31931.29</v>
       </c>
       <c r="U50" t="n">
         <v>0</v>
@@ -4501,31 +4485,31 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FBA79109</t>
+          <t>FBA79105</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AM-W18</t>
+          <t>AI-12</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>B0CM9HYVDM</t>
+          <t>B0CM6WH4ZT</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>B0CM9HYVDM</t>
+          <t>B0CM6WH4ZT</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AM-W18</t>
+          <t>AI-12</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>354</v>
+        <v>934</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -4537,7 +4521,7 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>534</v>
+        <v>1264</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -4555,7 +4539,7 @@
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -4567,7 +4551,7 @@
         <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>14001.67</v>
+        <v>9357.629999999999</v>
       </c>
       <c r="U51" t="n">
         <v>0</v>
@@ -4582,31 +4566,31 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>FBA79106</t>
+          <t>FBA79109</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>AM-C44</t>
+          <t>AM-W18</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>B0CM9KJZWQ</t>
+          <t>B0CM9HYVDM</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>B0CM9KJZWQ</t>
+          <t>B0CM9HYVDM</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AM-C44</t>
+          <t>AM-W18</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>340</v>
+        <v>354</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -4618,7 +4602,7 @@
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>440</v>
+        <v>534</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -4636,7 +4620,7 @@
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -4648,7 +4632,7 @@
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>14001.67</v>
       </c>
       <c r="U52" t="n">
         <v>0</v>
@@ -4663,31 +4647,31 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FBA79108</t>
+          <t>FBA79106</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>AM-W16</t>
+          <t>AM-C44</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>B0CM9L1QZG</t>
+          <t>B0CM9KJZWQ</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>B0CM9L1QZG</t>
+          <t>B0CM9KJZWQ</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AM-W16</t>
+          <t>AM-C44</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>47</v>
+        <v>340</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -4699,7 +4683,7 @@
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>66</v>
+        <v>440</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -4717,7 +4701,7 @@
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -4729,7 +4713,7 @@
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>3217.8</v>
+        <v>3982.2</v>
       </c>
       <c r="U53" t="n">
         <v>0</v>
@@ -4744,31 +4728,31 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FBA79107</t>
+          <t>FBA79108</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>AM-W17</t>
+          <t>AM-W16</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>B0CM9P5CCK</t>
+          <t>B0CM9L1QZG</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>B0CM9P5CCK</t>
+          <t>B0CM9L1QZG</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AM-W17</t>
+          <t>AM-W16</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>161</v>
+        <v>47</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -4780,7 +4764,7 @@
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>224</v>
+        <v>66</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -4798,7 +4782,7 @@
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -4810,7 +4794,7 @@
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>1439.83</v>
+        <v>3217.8</v>
       </c>
       <c r="U54" t="n">
         <v>0</v>
@@ -4825,31 +4809,31 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FBA79230</t>
+          <t>FBA79107</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>AM-W46</t>
+          <t>AM-W17</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>B0CX1XK5R6</t>
+          <t>B0CM9P5CCK</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>B0CX1XK5R6</t>
+          <t>B0CM9P5CCK</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AM-W46</t>
+          <t>AM-W17</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -4861,7 +4845,7 @@
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>133</v>
+        <v>224</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
@@ -4879,7 +4863,7 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -4891,7 +4875,7 @@
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>4319.51</v>
       </c>
       <c r="U55" t="n">
         <v>0</v>
@@ -4906,31 +4890,31 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FBA79379</t>
+          <t>FBA79230</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>AM-C45</t>
+          <t>AM-W46</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>B0D3LZWTHV</t>
+          <t>B0CX1XK5R6</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>B0D3LZWTHV</t>
+          <t>B0CX1XK5R6</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AM-C45</t>
+          <t>AM-W46</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>281</v>
+        <v>110</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -4942,7 +4926,7 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>419</v>
+        <v>133</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -4960,7 +4944,7 @@
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -4972,7 +4956,7 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>5845.76</v>
+        <v>0</v>
       </c>
       <c r="U56" t="n">
         <v>0</v>
@@ -4987,31 +4971,31 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FBA79380</t>
+          <t>FBA79379</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>AM-C46</t>
+          <t>AM-C45</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>B0D3M1B4Z8</t>
+          <t>B0D3LZWTHV</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>B0D3M1B4Z8</t>
+          <t>B0D3LZWTHV</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AM-C46</t>
+          <t>AM-C45</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1469</v>
+        <v>281</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -5023,7 +5007,7 @@
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>1836</v>
+        <v>419</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -5041,7 +5025,7 @@
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -5053,7 +5037,7 @@
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>70748.25999999999</v>
+        <v>8768.639999999999</v>
       </c>
       <c r="U57" t="n">
         <v>0</v>
@@ -5068,31 +5052,31 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FBA79355</t>
+          <t>FBA79380</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>AA-19BL</t>
+          <t>AM-C46</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>B0D3M86SH1</t>
+          <t>B0D3M1B4Z8</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>B0D3M86SH1</t>
+          <t>B0D3M1B4Z8</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AA-19BL</t>
+          <t>AM-C46</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1170</v>
+        <v>1469</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -5104,7 +5088,7 @@
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>1378</v>
+        <v>1836</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -5122,7 +5106,7 @@
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -5134,7 +5118,7 @@
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>21350.83</v>
+        <v>82609.29000000001</v>
       </c>
       <c r="U58" t="n">
         <v>0</v>
@@ -5149,31 +5133,31 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FBA79356</t>
+          <t>FBA79355</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>AA-19WL</t>
+          <t>AA-19BL</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>B0D3Q2T5XX</t>
+          <t>B0D3M86SH1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>B0D3Q2T5XX</t>
+          <t>B0D3M86SH1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AA-19WL</t>
+          <t>AA-19BL</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>229</v>
+        <v>1170</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -5185,7 +5169,7 @@
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>265</v>
+        <v>1378</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -5203,7 +5187,7 @@
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -5215,7 +5199,7 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>7625.42</v>
+        <v>21350.83</v>
       </c>
       <c r="U59" t="n">
         <v>0</v>
@@ -5230,31 +5214,31 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FBA79448</t>
+          <t>FBA79356</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>AM-W35</t>
+          <t>AA-19WL</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>B0DFMKY4TT</t>
+          <t>B0D3Q2T5XX</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>B0DFMKY4TT</t>
+          <t>B0D3Q2T5XX</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AM-W35</t>
+          <t>AA-19WL</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>302</v>
+        <v>229</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -5266,7 +5250,7 @@
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>378</v>
+        <v>265</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -5284,7 +5268,7 @@
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -5296,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>2880.51</v>
+        <v>7625.42</v>
       </c>
       <c r="U60" t="n">
         <v>0</v>
@@ -5311,31 +5295,31 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FBA79444</t>
+          <t>FBA79448</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>AM-W20</t>
+          <t>AM-W35</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>B0DFMLQBMC</t>
+          <t>B0DFMKY4TT</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>B0DFMLQBMC</t>
+          <t>B0DFMKY4TT</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AM-W20</t>
+          <t>AM-W35</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>14</v>
+        <v>302</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -5347,7 +5331,7 @@
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>16</v>
+        <v>378</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -5365,7 +5349,7 @@
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -5377,7 +5361,7 @@
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>0</v>
+        <v>2880.51</v>
       </c>
       <c r="U61" t="n">
         <v>0</v>
@@ -5392,31 +5376,31 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FBA79445</t>
+          <t>FBA79444</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AM-W32</t>
+          <t>AM-W20</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>B0DFMLS8JG</t>
+          <t>B0DFMLQBMC</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>B0DFMLS8JG</t>
+          <t>B0DFMLQBMC</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AM-W32</t>
+          <t>AM-W20</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>376</v>
+        <v>14</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -5428,7 +5412,7 @@
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>510</v>
+        <v>16</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
@@ -5446,7 +5430,7 @@
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -5458,7 +5442,7 @@
         <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>3388.98</v>
+        <v>0</v>
       </c>
       <c r="U62" t="n">
         <v>0</v>
@@ -5473,31 +5457,31 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FBA79447</t>
+          <t>FBA79445</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AM-W34</t>
+          <t>AM-W32</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>B0DFMLXD9S</t>
+          <t>B0DFMLS8JG</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>B0DFMLXD9S</t>
+          <t>B0DFMLS8JG</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AM-W34</t>
+          <t>AM-W32</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>282</v>
+        <v>376</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -5509,7 +5493,7 @@
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>404</v>
+        <v>510</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -5527,7 +5511,7 @@
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -5539,7 +5523,7 @@
         <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>13047.46</v>
+        <v>3388.98</v>
       </c>
       <c r="U63" t="n">
         <v>0</v>
@@ -5554,31 +5538,31 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>FBA79446</t>
+          <t>FBA79447</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AM-W33</t>
+          <t>AM-W34</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>B0DFMMTWLY</t>
+          <t>B0DFMLXD9S</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>B0DFMMTWLY</t>
+          <t>B0DFMLXD9S</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AM-W33</t>
+          <t>AM-W34</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>104</v>
+        <v>282</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -5590,7 +5574,7 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>150</v>
+        <v>404</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -5608,7 +5592,7 @@
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -5620,7 +5604,7 @@
         <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>20888.13</v>
+        <v>13047.46</v>
       </c>
       <c r="U64" t="n">
         <v>0</v>
@@ -5635,31 +5619,31 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FBA79449</t>
+          <t>FBA79446</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>AM-W36</t>
+          <t>AM-W33</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>B0DFMNGFTD</t>
+          <t>B0DFMMTWLY</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>B0DFMNGFTD</t>
+          <t>B0DFMMTWLY</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AM-W36</t>
+          <t>AM-W33</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>225</v>
+        <v>104</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -5671,7 +5655,7 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>282</v>
+        <v>150</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -5689,7 +5673,7 @@
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -5701,7 +5685,7 @@
         <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>22751.69</v>
       </c>
       <c r="U65" t="n">
         <v>0</v>
@@ -5716,31 +5700,31 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FBA79465</t>
+          <t>FBA79449</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>AM-W21</t>
+          <t>AM-W36</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>B0DFMQCGT1</t>
+          <t>B0DFMNGFTD</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>B0DFMQCGT1</t>
+          <t>B0DFMNGFTD</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AM-W21</t>
+          <t>AM-W36</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>101</v>
+        <v>225</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -5752,7 +5736,7 @@
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>117</v>
+        <v>282</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -5770,7 +5754,7 @@
         <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -5782,7 +5766,7 @@
         <v>0</v>
       </c>
       <c r="T66" t="n">
-        <v>0</v>
+        <v>5338.14</v>
       </c>
       <c r="U66" t="n">
         <v>0</v>
@@ -5797,31 +5781,31 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>FBA79653</t>
+          <t>FBA79465</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>AM-C45 Pro</t>
+          <t>AM-W21</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>B0DN6LJZBR</t>
+          <t>B0DFMQCGT1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>B0DN6LJZBR</t>
+          <t>B0DFMQCGT1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AM-C45 Pro</t>
+          <t>AM-W21</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>132</v>
+        <v>101</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -5833,7 +5817,7 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>169</v>
+        <v>117</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -5851,7 +5835,7 @@
         <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -5863,7 +5847,7 @@
         <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>3388.98</v>
+        <v>0</v>
       </c>
       <c r="U67" t="n">
         <v>0</v>
@@ -5878,31 +5862,31 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>FBA79654</t>
+          <t>FBA79653</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>AM-C11 Pro</t>
+          <t>AM-C45 Pro</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>B0DN6MNS1X</t>
+          <t>B0DN6LJZBR</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>B0DN6MNS1X</t>
+          <t>B0DN6LJZBR</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AM-C11 Pro</t>
+          <t>AM-C45 Pro</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>190</v>
+        <v>132</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -5914,7 +5898,7 @@
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>261</v>
+        <v>169</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -5944,7 +5928,7 @@
         <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>4405.93</v>
+        <v>3388.98</v>
       </c>
       <c r="U68" t="n">
         <v>0</v>
@@ -5959,31 +5943,31 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>FBA79655</t>
+          <t>FBA79654</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>AM-C44 Pro</t>
+          <t>AM-C11 Pro</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>B0DN6PFWNK</t>
+          <t>B0DN6MNS1X</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>B0DN6PFWNK</t>
+          <t>B0DN6MNS1X</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AM-C44 Pro</t>
+          <t>AM-C11 Pro</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>324</v>
+        <v>190</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -5995,7 +5979,7 @@
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>383</v>
+        <v>261</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -6013,7 +5997,7 @@
         <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -6025,7 +6009,7 @@
         <v>0</v>
       </c>
       <c r="T69" t="n">
-        <v>0</v>
+        <v>4405.93</v>
       </c>
       <c r="U69" t="n">
         <v>0</v>
@@ -6040,31 +6024,31 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FBA79694</t>
+          <t>FBA79655</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>AA-26</t>
+          <t>AM-C44 Pro</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>B0DT6T6N6B</t>
+          <t>B0DN6PFWNK</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>B0DT6T6N6B</t>
+          <t>B0DN6PFWNK</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AA-26</t>
+          <t>AM-C44 Pro</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1578</v>
+        <v>324</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -6076,7 +6060,7 @@
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>2277</v>
+        <v>383</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -6094,7 +6078,7 @@
         <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -6106,7 +6090,7 @@
         <v>0</v>
       </c>
       <c r="T70" t="n">
-        <v>32234.63</v>
+        <v>0</v>
       </c>
       <c r="U70" t="n">
         <v>0</v>
@@ -6121,31 +6105,31 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>FBA79482</t>
+          <t>FBA79694</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>AM-S1</t>
+          <t>AA-26</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>B0DXFPM4N2</t>
+          <t>B0DT6T6N6B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>B0DXFPM4N2</t>
+          <t>B0DT6T6N6B</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AM-S1</t>
+          <t>AA-26</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>7104</v>
+        <v>1578</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -6157,7 +6141,7 @@
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>10140</v>
+        <v>2277</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -6175,7 +6159,7 @@
         <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -6187,7 +6171,7 @@
         <v>0</v>
       </c>
       <c r="T71" t="n">
-        <v>501024.49</v>
+        <v>38833.77</v>
       </c>
       <c r="U71" t="n">
         <v>0</v>
@@ -6202,31 +6186,31 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>FBA79722</t>
+          <t>FBA79482</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>AM-W21</t>
+          <t>AM-S1</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>B0F2HYY7JF</t>
+          <t>B0DXFPM4N2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>B0F2HYY7JF</t>
+          <t>B0DXFPM4N2</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AM-W21</t>
+          <t>AM-S1</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>19</v>
+        <v>7104</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -6238,7 +6222,7 @@
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>23</v>
+        <v>10140</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
@@ -6256,7 +6240,7 @@
         <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
@@ -6268,7 +6252,7 @@
         <v>0</v>
       </c>
       <c r="T72" t="n">
-        <v>0</v>
+        <v>532048.21</v>
       </c>
       <c r="U72" t="n">
         <v>0</v>
@@ -6283,31 +6267,31 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>FBA79783</t>
+          <t>FBA79722</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>AM-C47</t>
+          <t>AM-W21</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>B0FF9R3GKK</t>
+          <t>B0F2HYY7JF</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>B0FF9R3GKK</t>
+          <t>B0F2HYY7JF</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AM-C47</t>
+          <t>AM-W21</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -6319,7 +6303,7 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>120</v>
+        <v>23</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -6364,31 +6348,31 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>FBA79708</t>
+          <t>FBA79783</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SB-01</t>
+          <t>AM-C47</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>B0FFB6YJM1</t>
+          <t>B0FF9R3GKK</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>B0FFB6YJM1</t>
+          <t>B0FF9R3GKK</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>SB-01</t>
+          <t>AM-C47</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>2158</v>
+        <v>95</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -6400,7 +6384,7 @@
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>2919</v>
+        <v>120</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
@@ -6418,7 +6402,7 @@
         <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -6430,7 +6414,7 @@
         <v>0</v>
       </c>
       <c r="T74" t="n">
-        <v>30506.74</v>
+        <v>0</v>
       </c>
       <c r="U74" t="n">
         <v>0</v>
@@ -6445,31 +6429,31 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>FBA79813</t>
+          <t>FBA79708</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>AH-50</t>
+          <t>SB-01</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>B0FG88HVQ8</t>
+          <t>B0FFB6YJM1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>B0FG88HVQ8</t>
+          <t>B0FFB6YJM1</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AH-50</t>
+          <t>SB-01</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>3119</v>
+        <v>2158</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -6481,7 +6465,7 @@
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>4695</v>
+        <v>2919</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
@@ -6499,7 +6483,7 @@
         <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>92</v>
+        <v>32</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -6511,7 +6495,7 @@
         <v>0</v>
       </c>
       <c r="T75" t="n">
-        <v>150455.37</v>
+        <v>33682.17</v>
       </c>
       <c r="U75" t="n">
         <v>0</v>
@@ -6526,31 +6510,31 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>FBA79825</t>
+          <t>FBA79813</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GB-02 (AM-C43 + AI-11)</t>
+          <t>AH-50</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>B0FJ2DT13L</t>
+          <t>B0FG88HVQ8</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>B0FJ2DT13L</t>
+          <t>B0FG88HVQ8</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>GB-02 (AM-C43 + AI-11)</t>
+          <t>AH-50</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>314</v>
+        <v>3119</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -6562,7 +6546,7 @@
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>450</v>
+        <v>4695</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -6580,7 +6564,7 @@
         <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>3</v>
+        <v>98</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
@@ -6592,7 +6576,7 @@
         <v>0</v>
       </c>
       <c r="T76" t="n">
-        <v>9658.469999999999</v>
+        <v>160955.37</v>
       </c>
       <c r="U76" t="n">
         <v>0</v>
@@ -6607,31 +6591,31 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>FBA79823</t>
+          <t>FBA79825</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PB-01 (AM-C11 + AI-04)</t>
+          <t>GB-02 (AM-C43 + AI-11)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>B0FJ2HZCVN</t>
+          <t>B0FJ2DT13L</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>B0FJ2HZCVN</t>
+          <t>B0FJ2DT13L</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>PB-01 (AM-C11 + AI-04)</t>
+          <t>GB-02 (AM-C43 + AI-11)</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>40</v>
+        <v>314</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -6643,7 +6627,7 @@
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>45</v>
+        <v>450</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -6661,7 +6645,7 @@
         <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -6673,7 +6657,7 @@
         <v>0</v>
       </c>
       <c r="T77" t="n">
-        <v>0</v>
+        <v>9658.469999999999</v>
       </c>
       <c r="U77" t="n">
         <v>0</v>
@@ -6688,31 +6672,31 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>FBA79822</t>
+          <t>FBA79823</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>KB-01 (AM-W32 + AI-12)</t>
+          <t>PB-01 (AM-C11 + AI-04)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>B0FJ2J6MTF</t>
+          <t>B0FJ2HZCVN</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>B0FJ2J6MTF</t>
+          <t>B0FJ2HZCVN</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>KB-01 (AM-W32 + AI-12)</t>
+          <t>PB-01 (AM-C11 + AI-04)</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -6724,7 +6708,7 @@
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
@@ -6769,31 +6753,31 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>FBA79821</t>
+          <t>FBA79822</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>UB-01 (AI-04, AM-S1, AA-21, AM-C2)</t>
+          <t>KB-01 (AM-W32 + AI-12)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>B0FJ2JJZL3</t>
+          <t>B0FJ2J6MTF</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>B0FJ2JJZL3</t>
+          <t>B0FJ2J6MTF</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>UB-01 (AI-04, AM-S1, AA-21, AM-C2)</t>
+          <t>KB-01 (AM-W32 + AI-12)</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>1136</v>
+        <v>46</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -6805,7 +6789,7 @@
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>1331</v>
+        <v>57</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
@@ -6850,31 +6834,31 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>FBA79824</t>
+          <t>FBA79821</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GB-01 (AM-C43 +AI-10)</t>
+          <t>UB-01 (AI-04, AM-S1, AA-21, AM-C2)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>B0FJ2K95XT</t>
+          <t>B0FJ2JJZL3</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>B0FJ2K95XT</t>
+          <t>B0FJ2JJZL3</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>GB-01 (AM-C43 +AI-10)</t>
+          <t>UB-01 (AI-04, AM-S1, AA-21, AM-C2)</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>160</v>
+        <v>1136</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -6886,7 +6870,7 @@
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>196</v>
+        <v>1331</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -6904,7 +6888,7 @@
         <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -6916,7 +6900,7 @@
         <v>0</v>
       </c>
       <c r="T80" t="n">
-        <v>4490.68</v>
+        <v>0</v>
       </c>
       <c r="U80" t="n">
         <v>0</v>
@@ -6931,31 +6915,31 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>FBA79826</t>
+          <t>FBA79824</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PB-02 (AI-04 Red + AM-C11 + AA-05)</t>
+          <t>GB-01 (AM-C43 +AI-10)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>B0FJ2LQT7K</t>
+          <t>B0FJ2K95XT</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>B0FJ2LQT7K</t>
+          <t>B0FJ2K95XT</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>PB-02 (AI-04 Red + AM-C11 + AA-05)</t>
+          <t>GB-01 (AM-C43 +AI-10)</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>32</v>
+        <v>160</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -6967,7 +6951,7 @@
         <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>39</v>
+        <v>196</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
@@ -7012,31 +6996,31 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>FBA79833</t>
+          <t>FBA79826</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>PB-04 (AI-04 Red + AM-C44 x 2)</t>
+          <t>PB-02 (AI-04 Red + AM-C11 + AA-05)</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>B0FJ8PZ9H7</t>
+          <t>B0FJ2LQT7K</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>B0FJ8PZ9H7</t>
+          <t>B0FJ2LQT7K</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>PB-04 (AI-04 Red + AM-C44 x 2)</t>
+          <t>PB-02 (AI-04 Red + AM-C11 + AA-05)</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>156</v>
+        <v>32</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -7048,7 +7032,7 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>192</v>
+        <v>39</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -7093,31 +7077,31 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>FBA79832</t>
+          <t>FBA79833</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>GB-05 (AM-C43 + AI-06)</t>
+          <t>PB-04 (AI-04 Red + AM-C44 x 2)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>B0FJ8S53GW</t>
+          <t>B0FJ8PZ9H7</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>B0FJ8S53GW</t>
+          <t>B0FJ8PZ9H7</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>GB-05 (AM-C43 + AI-06)</t>
+          <t>PB-04 (AI-04 Red + AM-C44 x 2)</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>707</v>
+        <v>156</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -7129,7 +7113,7 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>878</v>
+        <v>192</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
@@ -7147,7 +7131,7 @@
         <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -7159,7 +7143,7 @@
         <v>0</v>
       </c>
       <c r="T83" t="n">
-        <v>0</v>
+        <v>11694.07</v>
       </c>
       <c r="U83" t="n">
         <v>0</v>
@@ -7174,31 +7158,31 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>FBA79827</t>
+          <t>FBA79832</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>PB-03 (AI-04 Red + AM-C11 x 2)</t>
+          <t>GB-05 (AM-C43 + AI-06)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>B0FJ8S5XJ8</t>
+          <t>B0FJ8S53GW</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>B0FJ8S5XJ8</t>
+          <t>B0FJ8S53GW</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>PB-03 (AI-04 Red + AM-C11 x 2)</t>
+          <t>GB-05 (AM-C43 + AI-06)</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>124</v>
+        <v>707</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -7210,7 +7194,7 @@
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>153</v>
+        <v>878</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -7255,31 +7239,31 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>FBA79834</t>
+          <t>FBA79827</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>PB-05 (AA-05 + AM-C11 + AI-04)</t>
+          <t>PB-03 (AI-04 Red + AM-C11 x 2)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>B0FJ8T4WXM</t>
+          <t>B0FJ8S5XJ8</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>B0FJ8T4WXM</t>
+          <t>B0FJ8S5XJ8</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>PB-05 (AA-05 + AM-C11 + AI-04)</t>
+          <t>PB-03 (AI-04 Red + AM-C11 x 2)</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>15</v>
+        <v>124</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -7291,7 +7275,7 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>16</v>
+        <v>153</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
@@ -7336,31 +7320,31 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>FBA79830</t>
+          <t>FBA79834</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GB-03 (AI-12 + AM-C43)</t>
+          <t>PB-05 (AA-05 + AM-C11 + AI-04)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>B0FJ8TSQK1</t>
+          <t>B0FJ8T4WXM</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>B0FJ8TSQK1</t>
+          <t>B0FJ8T4WXM</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>GB-03 (AI-12 + AM-C43)</t>
+          <t>PB-05 (AA-05 + AM-C11 + AI-04)</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>496</v>
+        <v>15</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -7372,7 +7356,7 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>763</v>
+        <v>16</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -7390,7 +7374,7 @@
         <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -7402,7 +7386,7 @@
         <v>0</v>
       </c>
       <c r="T86" t="n">
-        <v>15934.73</v>
+        <v>0</v>
       </c>
       <c r="U86" t="n">
         <v>0</v>
@@ -7417,31 +7401,31 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>FBA79835</t>
+          <t>FBA79830</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>PB-06 (AA-05 + AM-C44 + AI-04)</t>
+          <t>GB-03 (AI-12 + AM-C43)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>B0FJ8TWCQZ</t>
+          <t>B0FJ8TSQK1</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>B0FJ8TWCQZ</t>
+          <t>B0FJ8TSQK1</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>PB-06 (AA-05 + AM-C44 + AI-04)</t>
+          <t>GB-03 (AI-12 + AM-C43)</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>11</v>
+        <v>496</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -7453,7 +7437,7 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>11</v>
+        <v>763</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -7471,7 +7455,7 @@
         <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
@@ -7483,7 +7467,7 @@
         <v>0</v>
       </c>
       <c r="T87" t="n">
-        <v>0</v>
+        <v>26609.29</v>
       </c>
       <c r="U87" t="n">
         <v>0</v>
@@ -7498,31 +7482,31 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>FBA79831</t>
+          <t>FBA79835</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>GB-04 (AM-C45 + AI-06)</t>
+          <t>PB-06 (AA-05 + AM-C44 + AI-04)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>B0FJ8W5Y9Q</t>
+          <t>B0FJ8TWCQZ</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>B0FJ8W5Y9Q</t>
+          <t>B0FJ8TWCQZ</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>GB-04 (AM-C45 + AI-06)</t>
+          <t>PB-06 (AA-05 + AM-C44 + AI-04)</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -7534,7 +7518,7 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -7579,31 +7563,31 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>FBA79836</t>
+          <t>FBA79831</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PB-07 (AA-05 + AM-C45 + AI-04)</t>
+          <t>GB-04 (AM-C45 + AI-06)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>B0FJ8Z1W81</t>
+          <t>B0FJ8W5Y9Q</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>B0FJ8Z1W81</t>
+          <t>B0FJ8W5Y9Q</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>PB-07 (AA-05 + AM-C45 + AI-04)</t>
+          <t>GB-04 (AM-C45 + AI-06)</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -7615,7 +7599,7 @@
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -7660,31 +7644,31 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>FBM79783</t>
+          <t>FBA79836</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>AM-C47</t>
+          <t>PB-07 (AA-05 + AM-C45 + AI-04)</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>B0FJS57732</t>
+          <t>B0FJ8Z1W81</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>B0FJS57732</t>
+          <t>B0FJ8Z1W81</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AM-C47</t>
+          <t>PB-07 (AA-05 + AM-C45 + AI-04)</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -7696,7 +7680,7 @@
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="K90" t="n">
         <v>0</v>
@@ -7741,31 +7725,31 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>FBK79708</t>
+          <t>FBM79783</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SB-01</t>
+          <t>AM-C47</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>B0FJS7JZ4V</t>
+          <t>B0FJS57732</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>B0FJS7JZ4V</t>
+          <t>B0FJS57732</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>SB-01</t>
+          <t>AM-C47</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -7777,7 +7761,7 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -7795,7 +7779,7 @@
         <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -7807,7 +7791,7 @@
         <v>0</v>
       </c>
       <c r="T91" t="n">
-        <v>1016.1</v>
+        <v>0</v>
       </c>
       <c r="U91" t="n">
         <v>0</v>
@@ -7822,31 +7806,31 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>FBK79009</t>
+          <t>FBK79708</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>AM-C41</t>
+          <t>SB-01</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>B0FLYHJ6DK</t>
+          <t>B0FJS7JZ4V</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>B0FLYHJ6DK</t>
+          <t>B0FJS7JZ4V</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AM-C41</t>
+          <t>SB-01</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>84</v>
+        <v>32</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -7858,7 +7842,7 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>144</v>
+        <v>45</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -7876,7 +7860,7 @@
         <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -7888,7 +7872,7 @@
         <v>0</v>
       </c>
       <c r="T92" t="n">
-        <v>2667.79</v>
+        <v>1016.1</v>
       </c>
       <c r="U92" t="n">
         <v>0</v>
@@ -7903,31 +7887,31 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>FBK79010</t>
+          <t>FBK79009</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>AM-C42</t>
+          <t>AM-C41</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>B0FLYJFC22</t>
+          <t>B0FLYHJ6DK</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>B0FLYJFC22</t>
+          <t>B0FLYHJ6DK</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AM-C42</t>
+          <t>AM-C41</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -7939,7 +7923,7 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -7969,7 +7953,7 @@
         <v>0</v>
       </c>
       <c r="T93" t="n">
-        <v>1986.44</v>
+        <v>2667.79</v>
       </c>
       <c r="U93" t="n">
         <v>0</v>
@@ -7984,31 +7968,31 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>FBA79845</t>
+          <t>FBK79010</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>UB-02 (AM-S1 + AA-21)</t>
+          <t>AM-C42</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>B0FN7B3KWS</t>
+          <t>B0FLYJFC22</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>B0FN7B3KWS</t>
+          <t>B0FLYJFC22</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>UB-02 (AM-S1 + AA-21)</t>
+          <t>AM-C42</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>2552</v>
+        <v>86</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -8020,7 +8004,7 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>3130</v>
+        <v>106</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -8038,7 +8022,7 @@
         <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -8050,7 +8034,7 @@
         <v>0</v>
       </c>
       <c r="T94" t="n">
-        <v>50758.46</v>
+        <v>1986.44</v>
       </c>
       <c r="U94" t="n">
         <v>0</v>
@@ -8065,31 +8049,31 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>FBA79846</t>
+          <t>FBA79845</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>AM-C11X Pro</t>
+          <t>UB-02 (AM-S1 + AA-21)</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>B0FN7C25VS</t>
+          <t>B0FN7B3KWS</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>B0FN7C25VS</t>
+          <t>B0FN7B3KWS</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AM-C11X Pro</t>
+          <t>UB-02 (AM-S1 + AA-21)</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>66</v>
+        <v>2552</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -8101,7 +8085,7 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>83</v>
+        <v>3130</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -8119,7 +8103,7 @@
         <v>0</v>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -8131,7 +8115,7 @@
         <v>0</v>
       </c>
       <c r="T95" t="n">
-        <v>0</v>
+        <v>61774.56</v>
       </c>
       <c r="U95" t="n">
         <v>0</v>
@@ -8146,31 +8130,31 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>FBA79847</t>
+          <t>FBA79846</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PB-09 (AM-C45 + AI-06 + AA-05)</t>
+          <t>AM-C11X Pro</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>B0FN7FYZM3</t>
+          <t>B0FN7C25VS</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>B0FN7FYZM3</t>
+          <t>B0FN7C25VS</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>PB-09 (AM-C45 + AI-06 + AA-05)</t>
+          <t>AM-C11X Pro</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -8182,7 +8166,7 @@
         <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
@@ -8227,31 +8211,31 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>FBA79815</t>
+          <t>FBA79847</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>AM-W19</t>
+          <t>PB-09 (AM-C45 + AI-06 + AA-05)</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>B0FPR7VFCH</t>
+          <t>B0FN7FYZM3</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>B0FPR7VFCH</t>
+          <t>B0FN7FYZM3</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AM-W19</t>
+          <t>PB-09 (AM-C45 + AI-06 + AA-05)</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>118</v>
+        <v>45</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -8263,7 +8247,7 @@
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>137</v>
+        <v>56</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
@@ -8308,31 +8292,31 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>FBA79816</t>
+          <t>FBA79815</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>AM-W22</t>
+          <t>AM-W19</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>B0FPR962YS</t>
+          <t>B0FPR7VFCH</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>B0FPR962YS</t>
+          <t>B0FPR7VFCH</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AM-W22</t>
+          <t>AM-W19</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>242</v>
+        <v>118</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -8344,7 +8328,7 @@
         <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>318</v>
+        <v>137</v>
       </c>
       <c r="K98" t="n">
         <v>0</v>
@@ -8389,31 +8373,31 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>FBA79841</t>
+          <t>FBA79816</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>AH-60-BL</t>
+          <t>AM-W22</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>B0FQBTRM28</t>
+          <t>B0FPR962YS</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>B0FQBTRM28</t>
+          <t>B0FPR962YS</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AH-60-BL</t>
+          <t>AM-W22</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>366</v>
+        <v>242</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -8425,7 +8409,7 @@
         <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>545</v>
+        <v>318</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
@@ -8443,7 +8427,7 @@
         <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -8455,7 +8439,7 @@
         <v>0</v>
       </c>
       <c r="T99" t="n">
-        <v>4966.94</v>
+        <v>0</v>
       </c>
       <c r="U99" t="n">
         <v>0</v>
@@ -8470,31 +8454,31 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>FBA79840</t>
+          <t>FBA79841</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>AH-60-RD</t>
+          <t>AH-60-BL</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>B0FQBWV1ST</t>
+          <t>B0FQBTRM28</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>B0FQBWV1ST</t>
+          <t>B0FQBTRM28</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AH-60-RD</t>
+          <t>AH-60-BL</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>287</v>
+        <v>366</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -8506,7 +8490,7 @@
         <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>391</v>
+        <v>545</v>
       </c>
       <c r="K100" t="n">
         <v>0</v>
@@ -8524,7 +8508,7 @@
         <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -8536,7 +8520,7 @@
         <v>0</v>
       </c>
       <c r="T100" t="n">
-        <v>10122.05</v>
+        <v>6661.01</v>
       </c>
       <c r="U100" t="n">
         <v>0</v>
@@ -8551,31 +8535,31 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>FBA79838</t>
+          <t>FBA79840</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>AH-40 SL</t>
+          <t>AH-60-RD</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>B0FQBX8J17</t>
+          <t>B0FQBWV1ST</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>B0FQBX8J17</t>
+          <t>B0FQBWV1ST</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AH-40 SL</t>
+          <t>AH-60-RD</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>738</v>
+        <v>287</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -8587,7 +8571,7 @@
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>1097</v>
+        <v>391</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>
@@ -8605,7 +8589,7 @@
         <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="Q101" t="n">
         <v>0</v>
@@ -8617,7 +8601,7 @@
         <v>0</v>
       </c>
       <c r="T101" t="n">
-        <v>25042.28</v>
+        <v>10122.05</v>
       </c>
       <c r="U101" t="n">
         <v>0</v>
@@ -8632,31 +8616,31 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>FBA79839</t>
+          <t>FBA79838</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>AH-45 BK</t>
+          <t>AH-40 SL</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>B0FQBXS6Y2</t>
+          <t>B0FQBX8J17</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>B0FQBXS6Y2</t>
+          <t>B0FQBX8J17</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AH-45 BK</t>
+          <t>AH-40 SL</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>1431</v>
+        <v>738</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -8668,7 +8652,7 @@
         <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>2176</v>
+        <v>1097</v>
       </c>
       <c r="K102" t="n">
         <v>0</v>
@@ -8686,7 +8670,7 @@
         <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="Q102" t="n">
         <v>0</v>
@@ -8698,7 +8682,7 @@
         <v>0</v>
       </c>
       <c r="T102" t="n">
-        <v>86975.23999999999</v>
+        <v>26288.89</v>
       </c>
       <c r="U102" t="n">
         <v>0</v>
@@ -8713,31 +8697,31 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>FBA79820</t>
+          <t>FBA79839</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>AC-3XL</t>
+          <t>AH-45 BK</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>B0FQJWWDVK</t>
+          <t>B0FQBXS6Y2</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>B0FQJWWDVK</t>
+          <t>B0FQBXS6Y2</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AC-3XL</t>
+          <t>AH-45 BK</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>132</v>
+        <v>1431</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -8749,7 +8733,7 @@
         <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>166</v>
+        <v>2176</v>
       </c>
       <c r="K103" t="n">
         <v>0</v>
@@ -8767,7 +8751,7 @@
         <v>0</v>
       </c>
       <c r="P103" t="n">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="Q103" t="n">
         <v>0</v>
@@ -8779,7 +8763,7 @@
         <v>0</v>
       </c>
       <c r="T103" t="n">
-        <v>3064.41</v>
+        <v>91511.69</v>
       </c>
       <c r="U103" t="n">
         <v>0</v>
@@ -8794,31 +8778,31 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>FBA79904</t>
+          <t>FBA79820</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PB-10 (AM-C2+AI-04+AH-60-BL)</t>
+          <t>AC-3XL</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>B0FTVQQVDC</t>
+          <t>B0FQJWWDVK</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>B0FTVQQVDC</t>
+          <t>B0FQJWWDVK</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>PB-10 (AM-C2+AI-04+AH-60-BL)</t>
+          <t>AC-3XL</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1536</v>
+        <v>132</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -8830,7 +8814,7 @@
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>2185</v>
+        <v>166</v>
       </c>
       <c r="K104" t="n">
         <v>0</v>
@@ -8860,7 +8844,7 @@
         <v>0</v>
       </c>
       <c r="T104" t="n">
-        <v>65831.36</v>
+        <v>3064.41</v>
       </c>
       <c r="U104" t="n">
         <v>0</v>
@@ -8875,31 +8859,31 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>FBA79905</t>
+          <t>FBA79904</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PB-11 (AM-C44+AA-05+AH-45-BK)</t>
+          <t>PB-10 (AM-C2+AI-04+AH-60-BL)</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>B0FTVSH458</t>
+          <t>B0FTVQQVDC</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>B0FTVSH458</t>
+          <t>B0FTVQQVDC</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>PB-11 (AM-C44+AA-05+AH-45-BK)</t>
+          <t>PB-10 (AM-C2+AI-04+AH-60-BL)</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>65</v>
+        <v>1536</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -8911,7 +8895,7 @@
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>80</v>
+        <v>2185</v>
       </c>
       <c r="K105" t="n">
         <v>0</v>
@@ -8929,7 +8913,7 @@
         <v>0</v>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q105" t="n">
         <v>0</v>
@@ -8941,7 +8925,7 @@
         <v>0</v>
       </c>
       <c r="T105" t="n">
-        <v>0</v>
+        <v>82778.81999999999</v>
       </c>
       <c r="U105" t="n">
         <v>0</v>
@@ -8956,31 +8940,31 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>FBA79908</t>
+          <t>FBA79905</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>PB-14 (AM-C43+AH-40-SL+AI-12)</t>
+          <t>PB-11 (AM-C44+AA-05+AH-45-BK)</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>B0FTVV1QJY</t>
+          <t>B0FTVSH458</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>B0FTVV1QJY</t>
+          <t>B0FTVSH458</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>PB-14 (AM-C43+AH-40-SL+AI-12)</t>
+          <t>PB-11 (AM-C44+AA-05+AH-45-BK)</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>278</v>
+        <v>65</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -8992,7 +8976,7 @@
         <v>0</v>
       </c>
       <c r="J106" t="n">
-        <v>372</v>
+        <v>80</v>
       </c>
       <c r="K106" t="n">
         <v>0</v>
@@ -9010,7 +8994,7 @@
         <v>0</v>
       </c>
       <c r="P106" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
         <v>0</v>
@@ -9022,7 +9006,7 @@
         <v>0</v>
       </c>
       <c r="T106" t="n">
-        <v>19148.31</v>
+        <v>0</v>
       </c>
       <c r="U106" t="n">
         <v>0</v>
@@ -9037,31 +9021,31 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>FBA79906</t>
+          <t>FBA79908</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>PB-12 (AM-C11+AA-05+AI-04+AH-60-RD)</t>
+          <t>PB-14 (AM-C43+AH-40-SL+AI-12)</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>B0FTVVLNS9</t>
+          <t>B0FTVV1QJY</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>B0FTVVLNS9</t>
+          <t>B0FTVV1QJY</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>PB-12 (AM-C11+AA-05+AI-04+AH-60-RD)</t>
+          <t>PB-14 (AM-C43+AH-40-SL+AI-12)</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>413</v>
+        <v>278</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -9073,7 +9057,7 @@
         <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>520</v>
+        <v>372</v>
       </c>
       <c r="K107" t="n">
         <v>0</v>
@@ -9091,7 +9075,7 @@
         <v>0</v>
       </c>
       <c r="P107" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q107" t="n">
         <v>0</v>
@@ -9103,7 +9087,7 @@
         <v>0</v>
       </c>
       <c r="T107" t="n">
-        <v>9321.190000000001</v>
+        <v>19148.31</v>
       </c>
       <c r="U107" t="n">
         <v>0</v>
@@ -9118,31 +9102,31 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>FBA79909</t>
+          <t>FBA79906</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>AM-W20</t>
+          <t>PB-12 (AM-C11+AA-05+AI-04+AH-60-RD)</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>B0FVM17Q4W</t>
+          <t>B0FTVVLNS9</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>B0FVM17Q4W</t>
+          <t>B0FTVVLNS9</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AM-W20</t>
+          <t>PB-12 (AM-C11+AA-05+AI-04+AH-60-RD)</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>28</v>
+        <v>413</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -9154,7 +9138,7 @@
         <v>0</v>
       </c>
       <c r="J108" t="n">
-        <v>48</v>
+        <v>520</v>
       </c>
       <c r="K108" t="n">
         <v>0</v>
@@ -9172,7 +9156,7 @@
         <v>0</v>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q108" t="n">
         <v>0</v>
@@ -9184,7 +9168,7 @@
         <v>0</v>
       </c>
       <c r="T108" t="n">
-        <v>0</v>
+        <v>9321.190000000001</v>
       </c>
       <c r="U108" t="n">
         <v>0</v>
@@ -9199,31 +9183,31 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>FBA79967</t>
+          <t>FBA79909</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>AM-W19</t>
+          <t>AM-W20</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>B0G2C2RCXN</t>
+          <t>B0FVM17Q4W</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>B0G2C2RCXN</t>
+          <t>B0FVM17Q4W</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AM-W19</t>
+          <t>AM-W20</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>263</v>
+        <v>28</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -9235,7 +9219,7 @@
         <v>0</v>
       </c>
       <c r="J109" t="n">
-        <v>349</v>
+        <v>48</v>
       </c>
       <c r="K109" t="n">
         <v>0</v>
@@ -9253,7 +9237,7 @@
         <v>0</v>
       </c>
       <c r="P109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q109" t="n">
         <v>0</v>
@@ -9265,7 +9249,7 @@
         <v>0</v>
       </c>
       <c r="T109" t="n">
-        <v>1694.07</v>
+        <v>0</v>
       </c>
       <c r="U109" t="n">
         <v>0</v>
@@ -9280,31 +9264,31 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>FBA79959</t>
+          <t>FBA79967</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>AM-W47 Wired</t>
+          <t>AM-W19</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>B0G39ZHDYP</t>
+          <t>B0G2C2RCXN</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>B0G39ZHDYP</t>
+          <t>B0G2C2RCXN</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AM-W47 Wired</t>
+          <t>AM-W19</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1321</v>
+        <v>263</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -9316,7 +9300,7 @@
         <v>0</v>
       </c>
       <c r="J110" t="n">
-        <v>1976</v>
+        <v>349</v>
       </c>
       <c r="K110" t="n">
         <v>0</v>
@@ -9334,7 +9318,7 @@
         <v>0</v>
       </c>
       <c r="P110" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="Q110" t="n">
         <v>0</v>
@@ -9346,7 +9330,7 @@
         <v>0</v>
       </c>
       <c r="T110" t="n">
-        <v>37011.87</v>
+        <v>1694.07</v>
       </c>
       <c r="U110" t="n">
         <v>0</v>
@@ -9361,31 +9345,31 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>FBA79960</t>
+          <t>FBA79959</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>AM-W47 Wireless</t>
+          <t>AM-W47 Wired</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>B0G3B152FR</t>
+          <t>B0G39ZHDYP</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>B0G3B152FR</t>
+          <t>B0G39ZHDYP</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AM-W47 Wireless</t>
+          <t>AM-W47 Wired</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>240</v>
+        <v>1321</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -9397,7 +9381,7 @@
         <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>385</v>
+        <v>1976</v>
       </c>
       <c r="K111" t="n">
         <v>0</v>
@@ -9415,7 +9399,7 @@
         <v>0</v>
       </c>
       <c r="P111" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="Q111" t="n">
         <v>0</v>
@@ -9427,7 +9411,7 @@
         <v>0</v>
       </c>
       <c r="T111" t="n">
-        <v>41560.99000000001</v>
+        <v>40060.17</v>
       </c>
       <c r="U111" t="n">
         <v>0</v>
@@ -9442,31 +9426,31 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>FBA79969</t>
+          <t>FBA79960</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>UB-03 (AM-S1 + AA-22)</t>
+          <t>AM-W47 Wireless</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>B0G3B677Z5</t>
+          <t>B0G3B152FR</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>B0G3B677Z5</t>
+          <t>B0G3B152FR</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>UB-03 (AM-S1 + AA-22)</t>
+          <t>AM-W47 Wireless</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>580</v>
+        <v>240</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -9478,7 +9462,7 @@
         <v>0</v>
       </c>
       <c r="J112" t="n">
-        <v>618</v>
+        <v>385</v>
       </c>
       <c r="K112" t="n">
         <v>0</v>
@@ -9496,7 +9480,7 @@
         <v>0</v>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Q112" t="n">
         <v>0</v>
@@ -9508,7 +9492,7 @@
         <v>0</v>
       </c>
       <c r="T112" t="n">
-        <v>0</v>
+        <v>44779.63</v>
       </c>
       <c r="U112" t="n">
         <v>0</v>
@@ -9523,31 +9507,31 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>FBA79957</t>
+          <t>FBA79969</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>AM-W23</t>
+          <t>UB-03 (AM-S1 + AA-22)</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>B0G3Q517Y2</t>
+          <t>B0G3B677Z5</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>B0G3Q517Y2</t>
+          <t>B0G3B677Z5</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AM-W23</t>
+          <t>UB-03 (AM-S1 + AA-22)</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>340</v>
+        <v>580</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -9559,7 +9543,7 @@
         <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>411</v>
+        <v>618</v>
       </c>
       <c r="K113" t="n">
         <v>0</v>
@@ -9604,31 +9588,31 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>FBA79958</t>
+          <t>FBA79957</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>AM-W24</t>
+          <t>AM-W23</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>B0G3Q59X8C</t>
+          <t>B0G3Q517Y2</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>B0G3Q59X8C</t>
+          <t>B0G3Q517Y2</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AM-W24</t>
+          <t>AM-W23</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>96</v>
+        <v>340</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -9640,7 +9624,7 @@
         <v>0</v>
       </c>
       <c r="J114" t="n">
-        <v>131</v>
+        <v>411</v>
       </c>
       <c r="K114" t="n">
         <v>0</v>
@@ -9658,7 +9642,7 @@
         <v>0</v>
       </c>
       <c r="P114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q114" t="n">
         <v>0</v>
@@ -9670,7 +9654,7 @@
         <v>0</v>
       </c>
       <c r="T114" t="n">
-        <v>1609.32</v>
+        <v>0</v>
       </c>
       <c r="U114" t="n">
         <v>0</v>
@@ -9685,31 +9669,31 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>FBA79842</t>
+          <t>FBA79958</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>AM-C48</t>
+          <t>AM-W24</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>B0G4DNF8RZ</t>
+          <t>B0G3Q59X8C</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>B0G4DNF8RZ</t>
+          <t>B0G3Q59X8C</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AM-C48</t>
+          <t>AM-W24</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>360</v>
+        <v>96</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -9721,7 +9705,7 @@
         <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>616</v>
+        <v>131</v>
       </c>
       <c r="K115" t="n">
         <v>0</v>
@@ -9739,7 +9723,7 @@
         <v>0</v>
       </c>
       <c r="P115" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Q115" t="n">
         <v>0</v>
@@ -9751,7 +9735,7 @@
         <v>0</v>
       </c>
       <c r="T115" t="n">
-        <v>24321.17</v>
+        <v>1609.32</v>
       </c>
       <c r="U115" t="n">
         <v>0</v>
@@ -9766,31 +9750,31 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>FBA79963</t>
+          <t>FBA79842</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>AM-Pro8</t>
+          <t>AM-C48</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>B0G53CB72D</t>
+          <t>B0G4DNF8RZ</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>B0G53CB72D</t>
+          <t>B0G4DNF8RZ</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AM-Pro8</t>
+          <t>AM-C48</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>104</v>
+        <v>360</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -9802,7 +9786,7 @@
         <v>0</v>
       </c>
       <c r="J116" t="n">
-        <v>142</v>
+        <v>616</v>
       </c>
       <c r="K116" t="n">
         <v>0</v>
@@ -9820,7 +9804,7 @@
         <v>0</v>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q116" t="n">
         <v>0</v>
@@ -9832,7 +9816,7 @@
         <v>0</v>
       </c>
       <c r="T116" t="n">
-        <v>0</v>
+        <v>27116.93</v>
       </c>
       <c r="U116" t="n">
         <v>0</v>
@@ -9847,31 +9831,31 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>FBA79961</t>
+          <t>FBA79963</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>AI-13</t>
+          <t>AM-Pro8</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>B0G53H49BS</t>
+          <t>B0G53CB72D</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>B0G53H49BS</t>
+          <t>B0G53CB72D</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AI-13</t>
+          <t>AM-Pro8</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>6412</v>
+        <v>104</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -9883,7 +9867,7 @@
         <v>0</v>
       </c>
       <c r="J117" t="n">
-        <v>8921</v>
+        <v>142</v>
       </c>
       <c r="K117" t="n">
         <v>0</v>
@@ -9901,7 +9885,7 @@
         <v>0</v>
       </c>
       <c r="P117" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
@@ -9913,7 +9897,7 @@
         <v>0</v>
       </c>
       <c r="T117" t="n">
-        <v>140146.87</v>
+        <v>0</v>
       </c>
       <c r="U117" t="n">
         <v>0</v>
@@ -9928,31 +9912,31 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>FBA79966</t>
+          <t>FBA79961</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>AM-Mix10</t>
+          <t>AI-13</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>B0G53KWRVW</t>
+          <t>B0G53H49BS</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>B0G53KWRVW</t>
+          <t>B0G53H49BS</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AM-Mix10</t>
+          <t>AI-13</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>244</v>
+        <v>6412</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -9964,7 +9948,7 @@
         <v>0</v>
       </c>
       <c r="J118" t="n">
-        <v>370</v>
+        <v>8921</v>
       </c>
       <c r="K118" t="n">
         <v>0</v>
@@ -9982,7 +9966,7 @@
         <v>0</v>
       </c>
       <c r="P118" t="n">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="Q118" t="n">
         <v>0</v>
@@ -9994,7 +9978,7 @@
         <v>0</v>
       </c>
       <c r="T118" t="n">
-        <v>16947.46</v>
+        <v>152735.87</v>
       </c>
       <c r="U118" t="n">
         <v>0</v>
@@ -10009,27 +9993,31 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>FBA79964</t>
+          <t>FBA79966</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>AM-Pro12</t>
+          <t>AM-Mix10</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>B0G53KWRWH</t>
+          <t>B0G53KWRVW</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>B0G53KWRWH</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr"/>
+          <t>B0G53KWRVW</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AM-Mix10</t>
+        </is>
+      </c>
       <c r="F119" t="n">
-        <v>0</v>
+        <v>244</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -10041,7 +10029,7 @@
         <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>0</v>
+        <v>370</v>
       </c>
       <c r="K119" t="n">
         <v>0</v>
@@ -10059,7 +10047,7 @@
         <v>0</v>
       </c>
       <c r="P119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q119" t="n">
         <v>0</v>
@@ -10071,7 +10059,7 @@
         <v>0</v>
       </c>
       <c r="T119" t="n">
-        <v>19405.93</v>
+        <v>16947.46</v>
       </c>
       <c r="U119" t="n">
         <v>0</v>
@@ -10086,31 +10074,27 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>FBA79962</t>
+          <t>FBA79964</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>BE-4T</t>
+          <t>AM-Pro12</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>B0G53LZNY3</t>
+          <t>B0G53KWRWH</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>B0G53LZNY3</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>BE-4T</t>
-        </is>
-      </c>
+          <t>B0G53KWRWH</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
-        <v>719</v>
+        <v>0</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -10122,7 +10106,7 @@
         <v>0</v>
       </c>
       <c r="J120" t="n">
-        <v>847</v>
+        <v>0</v>
       </c>
       <c r="K120" t="n">
         <v>0</v>
@@ -10140,7 +10124,7 @@
         <v>0</v>
       </c>
       <c r="P120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q120" t="n">
         <v>0</v>
@@ -10152,7 +10136,7 @@
         <v>0</v>
       </c>
       <c r="T120" t="n">
-        <v>8472.879999999999</v>
+        <v>19405.93</v>
       </c>
       <c r="U120" t="n">
         <v>0</v>
@@ -10167,31 +10151,31 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>FBA79968</t>
+          <t>FBA79962</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>AI-14</t>
+          <t>BE-4T</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>B0G53M9258</t>
+          <t>B0G53LZNY3</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>B0G53M9258</t>
+          <t>B0G53LZNY3</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AI-14</t>
+          <t>BE-4T</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>5849</v>
+        <v>719</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -10203,7 +10187,7 @@
         <v>0</v>
       </c>
       <c r="J121" t="n">
-        <v>7925</v>
+        <v>847</v>
       </c>
       <c r="K121" t="n">
         <v>0</v>
@@ -10221,7 +10205,7 @@
         <v>0</v>
       </c>
       <c r="P121" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="Q121" t="n">
         <v>0</v>
@@ -10233,7 +10217,7 @@
         <v>0</v>
       </c>
       <c r="T121" t="n">
-        <v>143831.39</v>
+        <v>8472.879999999999</v>
       </c>
       <c r="U121" t="n">
         <v>0</v>
@@ -10248,31 +10232,31 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>FBA79965</t>
+          <t>FBA79968</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>AM-Mix6</t>
+          <t>AI-14</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>B0G53PRM34</t>
+          <t>B0G53M9258</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>B0G53PRM34</t>
+          <t>B0G53M9258</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AM-Mix6</t>
+          <t>AI-14</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>647</v>
+        <v>5849</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -10284,7 +10268,7 @@
         <v>0</v>
       </c>
       <c r="J122" t="n">
-        <v>837</v>
+        <v>7925</v>
       </c>
       <c r="K122" t="n">
         <v>0</v>
@@ -10302,7 +10286,7 @@
         <v>0</v>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Q122" t="n">
         <v>0</v>
@@ -10314,7 +10298,7 @@
         <v>0</v>
       </c>
       <c r="T122" t="n">
-        <v>0</v>
+        <v>143831.39</v>
       </c>
       <c r="U122" t="n">
         <v>0</v>
@@ -10329,31 +10313,31 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>FBA79972</t>
+          <t>FBA79965</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>AM-Mix6</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>B0GCP1J2HC</t>
+          <t>B0G53PRM34</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>B0GCP1J2HC</t>
+          <t>B0G53PRM34</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>M8</t>
+          <t>AM-Mix6</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>3864</v>
+        <v>647</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -10365,7 +10349,7 @@
         <v>0</v>
       </c>
       <c r="J123" t="n">
-        <v>5465</v>
+        <v>837</v>
       </c>
       <c r="K123" t="n">
         <v>0</v>
@@ -10383,7 +10367,7 @@
         <v>0</v>
       </c>
       <c r="P123" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
         <v>0</v>
@@ -10395,7 +10379,7 @@
         <v>0</v>
       </c>
       <c r="T123" t="n">
-        <v>147707.62</v>
+        <v>0</v>
       </c>
       <c r="U123" t="n">
         <v>0</v>
@@ -10410,31 +10394,31 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>FBA79974</t>
+          <t>FBA79972</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>AM-S1</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>B0GD8JSPB1</t>
+          <t>B0GCP1J2HC</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>B0GD8JSPB1</t>
+          <t>B0GCP1J2HC</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AM-S1</t>
+          <t>M8</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>547</v>
+        <v>3864</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -10446,7 +10430,7 @@
         <v>0</v>
       </c>
       <c r="J124" t="n">
-        <v>774</v>
+        <v>5465</v>
       </c>
       <c r="K124" t="n">
         <v>0</v>
@@ -10464,7 +10448,7 @@
         <v>0</v>
       </c>
       <c r="P124" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="Q124" t="n">
         <v>0</v>
@@ -10476,7 +10460,7 @@
         <v>0</v>
       </c>
       <c r="T124" t="n">
-        <v>29233.9</v>
+        <v>147707.62</v>
       </c>
       <c r="U124" t="n">
         <v>0</v>
@@ -10491,31 +10475,31 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>FBA80016</t>
+          <t>FBA79974</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>AM-W22</t>
+          <t>AM-S1</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>B0GKPXQ8G3</t>
+          <t>B0GD8JSPB1</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>B0GKPXQ8G3</t>
+          <t>B0GD8JSPB1</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AM-W22</t>
+          <t>AM-S1</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>153</v>
+        <v>547</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -10527,7 +10511,7 @@
         <v>0</v>
       </c>
       <c r="J125" t="n">
-        <v>223</v>
+        <v>774</v>
       </c>
       <c r="K125" t="n">
         <v>0</v>
@@ -10545,7 +10529,7 @@
         <v>0</v>
       </c>
       <c r="P125" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q125" t="n">
         <v>0</v>
@@ -10557,7 +10541,7 @@
         <v>0</v>
       </c>
       <c r="T125" t="n">
-        <v>5761.02</v>
+        <v>29233.9</v>
       </c>
       <c r="U125" t="n">
         <v>0</v>
@@ -10572,31 +10556,31 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>FBA79956</t>
+          <t>FBA80016</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>A3-XLR</t>
+          <t>AM-W22</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>B0GMPGNXX3</t>
+          <t>B0GKPXQ8G3</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>B0GMPGNXX3</t>
+          <t>B0GKPXQ8G3</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>A3-XLR</t>
+          <t>AM-W22</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>23</v>
+        <v>153</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -10608,7 +10592,7 @@
         <v>0</v>
       </c>
       <c r="J126" t="n">
-        <v>34</v>
+        <v>223</v>
       </c>
       <c r="K126" t="n">
         <v>0</v>
@@ -10638,7 +10622,7 @@
         <v>0</v>
       </c>
       <c r="T126" t="n">
-        <v>1522.88</v>
+        <v>8641.52</v>
       </c>
       <c r="U126" t="n">
         <v>0</v>
@@ -10653,31 +10637,31 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>FBA80007</t>
+          <t>FBA79956</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>MT-12</t>
+          <t>A3-XLR</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>B0GN2LHJY4</t>
+          <t>B0GMPGNXX3</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>B0GN2LHJY4</t>
+          <t>B0GMPGNXX3</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>MT-12</t>
+          <t>A3-XLR</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>868</v>
+        <v>23</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -10689,7 +10673,7 @@
         <v>0</v>
       </c>
       <c r="J127" t="n">
-        <v>1272</v>
+        <v>34</v>
       </c>
       <c r="K127" t="n">
         <v>0</v>
@@ -10707,7 +10691,7 @@
         <v>0</v>
       </c>
       <c r="P127" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q127" t="n">
         <v>0</v>
@@ -10719,7 +10703,7 @@
         <v>0</v>
       </c>
       <c r="T127" t="n">
-        <v>52327.97</v>
+        <v>1522.88</v>
       </c>
       <c r="U127" t="n">
         <v>0</v>
@@ -10734,31 +10718,31 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>FBA79981</t>
+          <t>FBA80007</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>AK-61 Neo</t>
+          <t>MT-12</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>B0GN8MFDGZ</t>
+          <t>B0GN2LHJY4</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>B0GN8MFDGZ</t>
+          <t>B0GN2LHJY4</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AK-61 Neo</t>
+          <t>MT-12</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>489</v>
+        <v>868</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -10770,7 +10754,7 @@
         <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>730</v>
+        <v>1272</v>
       </c>
       <c r="K128" t="n">
         <v>0</v>
@@ -10788,7 +10772,7 @@
         <v>0</v>
       </c>
       <c r="P128" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q128" t="n">
         <v>0</v>
@@ -10800,7 +10784,7 @@
         <v>0</v>
       </c>
       <c r="T128" t="n">
-        <v>4066.94</v>
+        <v>59954.24000000001</v>
       </c>
       <c r="U128" t="n">
         <v>0</v>
@@ -10815,31 +10799,31 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>FBA79980</t>
+          <t>FBA79981</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>AK-37-W</t>
+          <t>AK-61 Neo</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>B0GN8MMKY1</t>
+          <t>B0GN8MFDGZ</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>B0GN8MMKY1</t>
+          <t>B0GN8MFDGZ</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AK-37-W</t>
+          <t>AK-61 Neo</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>343</v>
+        <v>489</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -10851,7 +10835,7 @@
         <v>0</v>
       </c>
       <c r="J129" t="n">
-        <v>453</v>
+        <v>730</v>
       </c>
       <c r="K129" t="n">
         <v>0</v>
@@ -10869,7 +10853,7 @@
         <v>0</v>
       </c>
       <c r="P129" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q129" t="n">
         <v>0</v>
@@ -10881,7 +10865,7 @@
         <v>0</v>
       </c>
       <c r="T129" t="n">
-        <v>6018.65</v>
+        <v>4066.94</v>
       </c>
       <c r="U129" t="n">
         <v>0</v>
@@ -10896,31 +10880,31 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>FBA79982</t>
+          <t>FBA79980</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>AK-61 Pro</t>
+          <t>AK-37-W</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>B0GN8MPYPG</t>
+          <t>B0GN8MMKY1</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>B0GN8MPYPG</t>
+          <t>B0GN8MMKY1</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AK-61 Pro</t>
+          <t>AK-37-W</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>579</v>
+        <v>343</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -10932,7 +10916,7 @@
         <v>0</v>
       </c>
       <c r="J130" t="n">
-        <v>820</v>
+        <v>453</v>
       </c>
       <c r="K130" t="n">
         <v>0</v>
@@ -10950,7 +10934,7 @@
         <v>0</v>
       </c>
       <c r="P130" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q130" t="n">
         <v>0</v>
@@ -10962,7 +10946,7 @@
         <v>0</v>
       </c>
       <c r="T130" t="n">
-        <v>0</v>
+        <v>6018.65</v>
       </c>
       <c r="U130" t="n">
         <v>0</v>
@@ -10977,31 +10961,31 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>FBA79979</t>
+          <t>FBA79982</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>AK-37-B</t>
+          <t>AK-61 Pro</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>B0GN8RQJRG</t>
+          <t>B0GN8MPYPG</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>B0GN8RQJRG</t>
+          <t>B0GN8MPYPG</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AK-37-B</t>
+          <t>AK-61 Pro</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>246</v>
+        <v>579</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -11013,7 +10997,7 @@
         <v>0</v>
       </c>
       <c r="J131" t="n">
-        <v>322</v>
+        <v>820</v>
       </c>
       <c r="K131" t="n">
         <v>0</v>
@@ -11031,7 +11015,7 @@
         <v>0</v>
       </c>
       <c r="P131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q131" t="n">
         <v>0</v>
@@ -11043,7 +11027,7 @@
         <v>0</v>
       </c>
       <c r="T131" t="n">
-        <v>423.73</v>
+        <v>9320.34</v>
       </c>
       <c r="U131" t="n">
         <v>0</v>
@@ -11058,31 +11042,31 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>FBA79848</t>
+          <t>FBA79979</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>AM-S2</t>
+          <t>AK-37-B</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>B0GN97RFPR</t>
+          <t>B0GN8RQJRG</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>B0GN97RFPR</t>
+          <t>B0GN8RQJRG</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AM-S2</t>
+          <t>AK-37-B</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>8290</v>
+        <v>246</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -11094,7 +11078,7 @@
         <v>0</v>
       </c>
       <c r="J132" t="n">
-        <v>11715</v>
+        <v>322</v>
       </c>
       <c r="K132" t="n">
         <v>0</v>
@@ -11112,7 +11096,7 @@
         <v>0</v>
       </c>
       <c r="P132" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="Q132" t="n">
         <v>0</v>
@@ -11124,7 +11108,7 @@
         <v>0</v>
       </c>
       <c r="T132" t="n">
-        <v>369199.78</v>
+        <v>423.73</v>
       </c>
       <c r="U132" t="n">
         <v>0</v>
@@ -11139,31 +11123,31 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>FBA79814</t>
+          <t>FBA79848</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>AH-50 Ear Cushion</t>
+          <t>AM-S2</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>B0GNM35G8X</t>
+          <t>B0GN97RFPR</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>B0GNM35G8X</t>
+          <t>B0GN97RFPR</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AH-50 Ear Cushion</t>
+          <t>AM-S2</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>10</v>
+        <v>8290</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -11175,7 +11159,7 @@
         <v>0</v>
       </c>
       <c r="J133" t="n">
-        <v>10</v>
+        <v>11715</v>
       </c>
       <c r="K133" t="n">
         <v>0</v>
@@ -11193,7 +11177,7 @@
         <v>0</v>
       </c>
       <c r="P133" t="n">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="Q133" t="n">
         <v>0</v>
@@ -11205,7 +11189,7 @@
         <v>0</v>
       </c>
       <c r="T133" t="n">
-        <v>912.62</v>
+        <v>401615.04</v>
       </c>
       <c r="U133" t="n">
         <v>0</v>
@@ -11220,31 +11204,31 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>FBA80009</t>
+          <t>FBA79814</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>AM-C51</t>
+          <t>AH-50 Ear Cushion</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>B0GW8R2RYM</t>
+          <t>B0GNM35G8X</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>B0GW8R2RYM</t>
+          <t>B0GNM35G8X</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AM-C51</t>
+          <t>AH-50 Ear Cushion</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -11256,7 +11240,7 @@
         <v>0</v>
       </c>
       <c r="J134" t="n">
-        <v>106</v>
+        <v>10</v>
       </c>
       <c r="K134" t="n">
         <v>0</v>
@@ -11274,7 +11258,7 @@
         <v>0</v>
       </c>
       <c r="P134" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q134" t="n">
         <v>0</v>
@@ -11286,7 +11270,7 @@
         <v>0</v>
       </c>
       <c r="T134" t="n">
-        <v>0</v>
+        <v>912.62</v>
       </c>
       <c r="U134" t="n">
         <v>0</v>
@@ -11301,31 +11285,31 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>FBA79995</t>
+          <t>FBA80009</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>AM-C50</t>
+          <t>AM-C51</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>B0GW8VBCBL</t>
+          <t>B0GW8R2RYM</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>B0GW8VBCBL</t>
+          <t>B0GW8R2RYM</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AM-C50</t>
+          <t>AM-C51</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -11337,7 +11321,7 @@
         <v>0</v>
       </c>
       <c r="J135" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K135" t="n">
         <v>0</v>
@@ -11355,7 +11339,7 @@
         <v>0</v>
       </c>
       <c r="P135" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q135" t="n">
         <v>0</v>
@@ -11367,7 +11351,7 @@
         <v>0</v>
       </c>
       <c r="T135" t="n">
-        <v>1502.54</v>
+        <v>0</v>
       </c>
       <c r="U135" t="n">
         <v>0</v>
@@ -11382,31 +11366,31 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>FBA80000</t>
+          <t>FBA79995</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>DP-718H</t>
+          <t>AM-C50</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>B0GW8XGPB2</t>
+          <t>B0GW8VBCBL</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>B0GW8XGPB2</t>
+          <t>B0GW8VBCBL</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>DP-718H</t>
+          <t>AM-C50</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -11418,7 +11402,7 @@
         <v>0</v>
       </c>
       <c r="J136" t="n">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="K136" t="n">
         <v>0</v>
@@ -11436,7 +11420,7 @@
         <v>0</v>
       </c>
       <c r="P136" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q136" t="n">
         <v>0</v>
@@ -11448,7 +11432,7 @@
         <v>0</v>
       </c>
       <c r="T136" t="n">
-        <v>0</v>
+        <v>1502.54</v>
       </c>
       <c r="U136" t="n">
         <v>0</v>
@@ -11463,31 +11447,31 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>FBA79998</t>
+          <t>FBA80000</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>DP-718H</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>B0GW8YC59C</t>
+          <t>B0GW8XGPB2</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>B0GW8YC59C</t>
+          <t>B0GW8XGPB2</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>DP-718H</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -11499,7 +11483,7 @@
         <v>0</v>
       </c>
       <c r="J137" t="n">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="K137" t="n">
         <v>0</v>
@@ -11544,31 +11528,31 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>FBA79996</t>
+          <t>FBA79998</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>AM-C49</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>B0GW8Z556N</t>
+          <t>B0GW8YC59C</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>B0GW8Z556N</t>
+          <t>B0GW8YC59C</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AM-C49</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>164</v>
+        <v>60</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -11580,7 +11564,7 @@
         <v>0</v>
       </c>
       <c r="J138" t="n">
-        <v>233</v>
+        <v>80</v>
       </c>
       <c r="K138" t="n">
         <v>0</v>
@@ -11598,7 +11582,7 @@
         <v>0</v>
       </c>
       <c r="P138" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q138" t="n">
         <v>0</v>
@@ -11610,7 +11594,7 @@
         <v>0</v>
       </c>
       <c r="T138" t="n">
-        <v>4401.71</v>
+        <v>0</v>
       </c>
       <c r="U138" t="n">
         <v>0</v>
@@ -11625,31 +11609,31 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>FBA80010</t>
+          <t>FBA79996</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>AM-C52</t>
+          <t>AM-C49</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>B0GW8ZQRFK</t>
+          <t>B0GW8Z556N</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>B0GW8ZQRFK</t>
+          <t>B0GW8Z556N</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AM-C52</t>
+          <t>AM-C49</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>36</v>
+        <v>164</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -11661,7 +11645,7 @@
         <v>0</v>
       </c>
       <c r="J139" t="n">
-        <v>53</v>
+        <v>233</v>
       </c>
       <c r="K139" t="n">
         <v>0</v>
@@ -11679,7 +11663,7 @@
         <v>0</v>
       </c>
       <c r="P139" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q139" t="n">
         <v>0</v>
@@ -11691,7 +11675,7 @@
         <v>0</v>
       </c>
       <c r="T139" t="n">
-        <v>0</v>
+        <v>4401.71</v>
       </c>
       <c r="U139" t="n">
         <v>0</v>
@@ -11706,31 +11690,31 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>FBA80004</t>
+          <t>FBA80010</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>AM-W36 Pro</t>
+          <t>AM-C52</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>B0GW92316G</t>
+          <t>B0GW8ZQRFK</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>B0GW92316G</t>
+          <t>B0GW8ZQRFK</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AM-W36 Pro</t>
+          <t>AM-C52</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -11742,7 +11726,7 @@
         <v>0</v>
       </c>
       <c r="J140" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="K140" t="n">
         <v>0</v>
@@ -11760,7 +11744,7 @@
         <v>0</v>
       </c>
       <c r="P140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q140" t="n">
         <v>0</v>
@@ -11772,7 +11756,7 @@
         <v>0</v>
       </c>
       <c r="T140" t="n">
-        <v>0</v>
+        <v>1355.08</v>
       </c>
       <c r="U140" t="n">
         <v>0</v>
@@ -11787,62 +11771,62 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>FBA80001</t>
+          <t>FBA80004</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>USB718</t>
+          <t>AM-W36 Pro</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>B0GW92TQGV</t>
+          <t>B0GW92316G</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>B0GW92TQGV</t>
+          <t>B0GW92316G</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>USB718</t>
+          <t>AM-W36 Pro</t>
         </is>
       </c>
       <c r="F141" t="n">
+        <v>43</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" t="n">
+        <v>64</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0</v>
+      </c>
+      <c r="P141" t="n">
         <v>1</v>
       </c>
-      <c r="G141" t="n">
-        <v>0</v>
-      </c>
-      <c r="H141" t="n">
-        <v>0</v>
-      </c>
-      <c r="I141" t="n">
-        <v>0</v>
-      </c>
-      <c r="J141" t="n">
-        <v>1</v>
-      </c>
-      <c r="K141" t="n">
-        <v>0</v>
-      </c>
-      <c r="L141" t="n">
-        <v>0</v>
-      </c>
-      <c r="M141" t="n">
-        <v>0</v>
-      </c>
-      <c r="N141" t="n">
-        <v>0</v>
-      </c>
-      <c r="O141" t="n">
-        <v>0</v>
-      </c>
-      <c r="P141" t="n">
-        <v>0</v>
-      </c>
       <c r="Q141" t="n">
         <v>0</v>
       </c>
@@ -11853,7 +11837,7 @@
         <v>0</v>
       </c>
       <c r="T141" t="n">
-        <v>0</v>
+        <v>6778.81</v>
       </c>
       <c r="U141" t="n">
         <v>0</v>
@@ -11868,31 +11852,31 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>FBA80003</t>
+          <t>FBA80001</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>AM-W32 Pro</t>
+          <t>USB718</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>B0GW92TTMS</t>
+          <t>B0GW92TQGV</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>B0GW92TTMS</t>
+          <t>B0GW92TQGV</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AM-W32 Pro</t>
+          <t>USB718</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -11904,7 +11888,7 @@
         <v>0</v>
       </c>
       <c r="J142" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="K142" t="n">
         <v>0</v>
@@ -11922,7 +11906,7 @@
         <v>0</v>
       </c>
       <c r="P142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q142" t="n">
         <v>0</v>
@@ -11934,7 +11918,7 @@
         <v>0</v>
       </c>
       <c r="T142" t="n">
-        <v>4872.03</v>
+        <v>0</v>
       </c>
       <c r="U142" t="n">
         <v>0</v>
@@ -11949,31 +11933,31 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>FBA79999</t>
+          <t>FBA80003</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>JTG800</t>
+          <t>AM-W32 Pro</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>B0GW92TVVC</t>
+          <t>B0GW92TTMS</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>B0GW92TVVC</t>
+          <t>B0GW92TTMS</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>JTG800</t>
+          <t>AM-W32 Pro</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -11985,7 +11969,7 @@
         <v>0</v>
       </c>
       <c r="J143" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="K143" t="n">
         <v>0</v>
@@ -12003,7 +11987,7 @@
         <v>0</v>
       </c>
       <c r="P143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q143" t="n">
         <v>0</v>
@@ -12015,7 +11999,7 @@
         <v>0</v>
       </c>
       <c r="T143" t="n">
-        <v>0</v>
+        <v>4872.03</v>
       </c>
       <c r="U143" t="n">
         <v>0</v>
@@ -12030,31 +12014,31 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>FBA80005</t>
+          <t>FBA79999</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>T-835</t>
+          <t>JTG800</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>B0GW96CQMG</t>
+          <t>B0GW92TVVC</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>B0GW96CQMG</t>
+          <t>B0GW92TVVC</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>T-835</t>
+          <t>JTG800</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -12066,7 +12050,7 @@
         <v>0</v>
       </c>
       <c r="J144" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="K144" t="n">
         <v>0</v>
@@ -12111,31 +12095,31 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>FBA80002</t>
+          <t>FBA80005</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>AM-W33 Pro</t>
+          <t>T-835</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>B0GW96SHSK</t>
+          <t>B0GW96CQMG</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>B0GW96SHSK</t>
+          <t>B0GW96CQMG</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AM-W33 Pro</t>
+          <t>T-835</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -12147,7 +12131,7 @@
         <v>0</v>
       </c>
       <c r="J145" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="K145" t="n">
         <v>0</v>
@@ -12192,31 +12176,31 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>FBA79975</t>
+          <t>FBA80002</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>AE831</t>
+          <t>AM-W33 Pro</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>B0GXP7LJ75</t>
+          <t>B0GW96SHSK</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>B0GXP7LJ75</t>
+          <t>B0GW96SHSK</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AE831</t>
+          <t>AM-W33 Pro</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -12228,7 +12212,7 @@
         <v>0</v>
       </c>
       <c r="J146" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="K146" t="n">
         <v>0</v>
@@ -12273,31 +12257,31 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>FBA80084</t>
+          <t>FBA79975</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>BE-4</t>
+          <t>AE831</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>B0GXP97CZG</t>
+          <t>B0GXP7LJ75</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>B0GXP97CZG</t>
+          <t>B0GXP7LJ75</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>BE-4</t>
+          <t>AE831</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>2224</v>
+        <v>21</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -12309,7 +12293,7 @@
         <v>0</v>
       </c>
       <c r="J147" t="n">
-        <v>3111</v>
+        <v>24</v>
       </c>
       <c r="K147" t="n">
         <v>0</v>
@@ -12327,7 +12311,7 @@
         <v>0</v>
       </c>
       <c r="P147" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q147" t="n">
         <v>0</v>
@@ -12339,7 +12323,7 @@
         <v>0</v>
       </c>
       <c r="T147" t="n">
-        <v>41368.64</v>
+        <v>0</v>
       </c>
       <c r="U147" t="n">
         <v>0</v>
@@ -12354,31 +12338,31 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>FBA80085</t>
+          <t>FBA80084</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>M6</t>
+          <t>BE-4</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>B0GXPBHDRF</t>
+          <t>B0GXP97CZG</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>B0GXPBHDRF</t>
+          <t>B0GXP97CZG</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>M6</t>
+          <t>BE-4</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>472</v>
+        <v>2224</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -12390,7 +12374,7 @@
         <v>0</v>
       </c>
       <c r="J148" t="n">
-        <v>601</v>
+        <v>3111</v>
       </c>
       <c r="K148" t="n">
         <v>0</v>
@@ -12408,7 +12392,7 @@
         <v>0</v>
       </c>
       <c r="P148" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="Q148" t="n">
         <v>0</v>
@@ -12420,7 +12404,7 @@
         <v>0</v>
       </c>
       <c r="T148" t="n">
-        <v>5931.36</v>
+        <v>38149.15</v>
       </c>
       <c r="U148" t="n">
         <v>0</v>
@@ -12435,31 +12419,31 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>FBA80075</t>
+          <t>FBA80085</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>PB-16 (AH-50+AI-13+AM-C2)</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>B0GXPGBQB1</t>
+          <t>B0GXPBHDRF</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>B0GXPGBQB1</t>
+          <t>B0GXPBHDRF</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>PB-16 (AH-50+AI-13+AM-C2)</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>15</v>
+        <v>472</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -12471,7 +12455,7 @@
         <v>0</v>
       </c>
       <c r="J149" t="n">
-        <v>18</v>
+        <v>601</v>
       </c>
       <c r="K149" t="n">
         <v>0</v>
@@ -12489,7 +12473,7 @@
         <v>0</v>
       </c>
       <c r="P149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q149" t="n">
         <v>0</v>
@@ -12501,7 +12485,7 @@
         <v>0</v>
       </c>
       <c r="T149" t="n">
-        <v>0</v>
+        <v>5931.36</v>
       </c>
       <c r="U149" t="n">
         <v>0</v>
@@ -12516,31 +12500,31 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>FBA80104</t>
+          <t>FBA80075</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>UB-04 (AM-S2+AA-21+AI-04+AM-C2)</t>
+          <t>PB-16 (AH-50+AI-13+AM-C2)</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>B0GXY7YJWP</t>
+          <t>B0GXPGBQB1</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>B0GXY7YJWP</t>
+          <t>B0GXPGBQB1</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>UB-04 (AM-S2+AA-21+AI-04+AM-C2)</t>
+          <t>PB-16 (AH-50+AI-13+AM-C2)</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>476</v>
+        <v>15</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -12552,7 +12536,7 @@
         <v>0</v>
       </c>
       <c r="J150" t="n">
-        <v>551</v>
+        <v>18</v>
       </c>
       <c r="K150" t="n">
         <v>0</v>
@@ -12570,7 +12554,7 @@
         <v>0</v>
       </c>
       <c r="P150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q150" t="n">
         <v>0</v>
@@ -12582,7 +12566,7 @@
         <v>0</v>
       </c>
       <c r="T150" t="n">
-        <v>16524.58</v>
+        <v>0</v>
       </c>
       <c r="U150" t="n">
         <v>0</v>
@@ -12597,31 +12581,31 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>FBA80074</t>
+          <t>FBA80104</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>PB-15 (AH-50+AM-C2+AI-04)</t>
+          <t>UB-04 (AM-S2+AA-21+AI-04+AM-C2)</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>B0GY827J9C</t>
+          <t>B0GXY7YJWP</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>B0GY827J9C</t>
+          <t>B0GXY7YJWP</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>PB-15 (AH-50+AM-C2+AI-04)</t>
+          <t>UB-04 (AM-S2+AA-21+AI-04+AM-C2)</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>0</v>
+        <v>476</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -12633,7 +12617,7 @@
         <v>0</v>
       </c>
       <c r="J151" t="n">
-        <v>0</v>
+        <v>551</v>
       </c>
       <c r="K151" t="n">
         <v>0</v>
@@ -12651,7 +12635,7 @@
         <v>0</v>
       </c>
       <c r="P151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q151" t="n">
         <v>0</v>
@@ -12663,7 +12647,7 @@
         <v>0</v>
       </c>
       <c r="T151" t="n">
-        <v>0</v>
+        <v>16524.58</v>
       </c>
       <c r="U151" t="n">
         <v>0</v>
@@ -12678,31 +12662,31 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>FBA80076</t>
+          <t>FBA80074</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>PB-17 (AH-40-SL+AM-C43+AI-13)</t>
+          <t>PB-15 (AH-50+AM-C2+AI-04)</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>B0GY857139</t>
+          <t>B0GY827J9C</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>B0GY857139</t>
+          <t>B0GY827J9C</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>PB-17 (AH-40-SL+AM-C43+AI-13)</t>
+          <t>PB-15 (AH-50+AM-C2+AI-04)</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -12714,7 +12698,7 @@
         <v>0</v>
       </c>
       <c r="J152" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K152" t="n">
         <v>0</v>
@@ -12759,31 +12743,31 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>FBA80077</t>
+          <t>FBA80076</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>PB-18 (AH-45-BK+AI-03+AM-C39)</t>
+          <t>PB-17 (AH-40-SL+AM-C43+AI-13)</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>B0GY86ZT1X</t>
+          <t>B0GY857139</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>B0GY86ZT1X</t>
+          <t>B0GY857139</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>PB-18 (AH-45-BK+AI-03+AM-C39)</t>
+          <t>PB-17 (AH-40-SL+AM-C43+AI-13)</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -12795,7 +12779,7 @@
         <v>0</v>
       </c>
       <c r="J153" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="K153" t="n">
         <v>0</v>
@@ -12840,31 +12824,31 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>FBA80128</t>
+          <t>FBA80077</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>AI-13</t>
+          <t>PB-18 (AH-45-BK+AI-03+AM-C39)</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>B0H1H3K6B2</t>
+          <t>B0GY86ZT1X</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>B0H1H3K6B2</t>
+          <t>B0GY86ZT1X</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AI-13</t>
+          <t>PB-18 (AH-45-BK+AI-03+AM-C39)</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>148</v>
+        <v>6</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -12876,7 +12860,7 @@
         <v>0</v>
       </c>
       <c r="J154" t="n">
-        <v>197</v>
+        <v>6</v>
       </c>
       <c r="K154" t="n">
         <v>0</v>
@@ -12894,7 +12878,7 @@
         <v>0</v>
       </c>
       <c r="P154" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q154" t="n">
         <v>0</v>
@@ -12906,7 +12890,7 @@
         <v>0</v>
       </c>
       <c r="T154" t="n">
-        <v>4489.83</v>
+        <v>0</v>
       </c>
       <c r="U154" t="n">
         <v>0</v>
@@ -12921,31 +12905,31 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>FBA80143</t>
+          <t>FBA80128</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>AM-S2</t>
+          <t>AI-13</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>B0H1MTP2ZP</t>
+          <t>B0H1H3K6B2</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>B0H1MTP2ZP</t>
+          <t>B0H1H3K6B2</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AM-S2</t>
+          <t>AI-13</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>113</v>
+        <v>148</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -12957,7 +12941,7 @@
         <v>0</v>
       </c>
       <c r="J155" t="n">
-        <v>137</v>
+        <v>197</v>
       </c>
       <c r="K155" t="n">
         <v>0</v>
@@ -12975,7 +12959,7 @@
         <v>0</v>
       </c>
       <c r="P155" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q155" t="n">
         <v>0</v>
@@ -12987,7 +12971,7 @@
         <v>0</v>
       </c>
       <c r="T155" t="n">
-        <v>0</v>
+        <v>4489.83</v>
       </c>
       <c r="U155" t="n">
         <v>0</v>
@@ -13002,31 +12986,31 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>FBA80106</t>
+          <t>FBA80143</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>UB-06 (AM-S2+AA-22)</t>
+          <t>AM-S2</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>B0H2FCK54H</t>
+          <t>B0H1MTP2ZP</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>B0H2FCK54H</t>
+          <t>B0H1MTP2ZP</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>UB-06 (AM-S2+AA-22)</t>
+          <t>AM-S2</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>441</v>
+        <v>113</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -13038,7 +13022,7 @@
         <v>0</v>
       </c>
       <c r="J156" t="n">
-        <v>481</v>
+        <v>137</v>
       </c>
       <c r="K156" t="n">
         <v>0</v>
@@ -13056,7 +13040,7 @@
         <v>0</v>
       </c>
       <c r="P156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q156" t="n">
         <v>0</v>
@@ -13068,7 +13052,7 @@
         <v>0</v>
       </c>
       <c r="T156" t="n">
-        <v>8727.969999999999</v>
+        <v>0</v>
       </c>
       <c r="U156" t="n">
         <v>0</v>
@@ -13083,31 +13067,31 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>FBA80105</t>
+          <t>FBA80106</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>UB-05 (AM-S2+AA-21)</t>
+          <t>UB-06 (AM-S2+AA-22)</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>B0H2FNV2RC</t>
+          <t>B0H2FCK54H</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>B0H2FNV2RC</t>
+          <t>B0H2FCK54H</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>UB-05 (AM-S2+AA-21)</t>
+          <t>UB-06 (AM-S2+AA-22)</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>492</v>
+        <v>441</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -13119,7 +13103,7 @@
         <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>564</v>
+        <v>481</v>
       </c>
       <c r="K157" t="n">
         <v>0</v>
@@ -13137,7 +13121,7 @@
         <v>0</v>
       </c>
       <c r="P157" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q157" t="n">
         <v>0</v>
@@ -13149,7 +13133,7 @@
         <v>0</v>
       </c>
       <c r="T157" t="n">
-        <v>26692.37</v>
+        <v>8727.969999999999</v>
       </c>
       <c r="U157" t="n">
         <v>0</v>
@@ -13164,31 +13148,31 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>FBA80110</t>
+          <t>FBA80105</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>X5</t>
+          <t>UB-05 (AM-S2+AA-21)</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>B0H2Z6R6V8</t>
+          <t>B0H2FNV2RC</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>B0H2Z6R6V8</t>
+          <t>B0H2FNV2RC</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>X5</t>
+          <t>UB-05 (AM-S2+AA-21)</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>117</v>
+        <v>492</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -13200,7 +13184,7 @@
         <v>0</v>
       </c>
       <c r="J158" t="n">
-        <v>146</v>
+        <v>564</v>
       </c>
       <c r="K158" t="n">
         <v>0</v>
@@ -13218,7 +13202,7 @@
         <v>0</v>
       </c>
       <c r="P158" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q158" t="n">
         <v>0</v>
@@ -13230,7 +13214,7 @@
         <v>0</v>
       </c>
       <c r="T158" t="n">
-        <v>0</v>
+        <v>26692.37</v>
       </c>
       <c r="U158" t="n">
         <v>0</v>
@@ -13245,31 +13229,31 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>FBA80109</t>
+          <t>FBA80110</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>X5</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>B0H2ZCQFTZ</t>
+          <t>B0H2Z6R6V8</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>B0H2ZCQFTZ</t>
+          <t>B0H2Z6R6V8</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>X5</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>392</v>
+        <v>117</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -13281,7 +13265,7 @@
         <v>0</v>
       </c>
       <c r="J159" t="n">
-        <v>524</v>
+        <v>146</v>
       </c>
       <c r="K159" t="n">
         <v>0</v>
@@ -13326,81 +13310,162 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
+          <t>FBA80109</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>B0H2ZCQFTZ</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>B0H2ZCQFTZ</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>392</v>
+      </c>
+      <c r="G160" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" t="n">
+        <v>0</v>
+      </c>
+      <c r="I160" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" t="n">
+        <v>524</v>
+      </c>
+      <c r="K160" t="n">
+        <v>0</v>
+      </c>
+      <c r="L160" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" t="n">
+        <v>0</v>
+      </c>
+      <c r="N160" t="n">
+        <v>0</v>
+      </c>
+      <c r="O160" t="n">
+        <v>0</v>
+      </c>
+      <c r="P160" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>0</v>
+      </c>
+      <c r="R160" t="n">
+        <v>0</v>
+      </c>
+      <c r="S160" t="n">
+        <v>0</v>
+      </c>
+      <c r="T160" t="n">
+        <v>0</v>
+      </c>
+      <c r="U160" t="n">
+        <v>0</v>
+      </c>
+      <c r="V160" t="n">
+        <v>0</v>
+      </c>
+      <c r="W160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
           <t>FBA80142</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr">
+      <c r="B161" t="inlineStr">
         <is>
           <t>AM-C5 White</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr">
+      <c r="C161" t="inlineStr">
         <is>
           <t>B0H3LHF2WW</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr">
+      <c r="D161" t="inlineStr">
         <is>
           <t>B0H3LHF2WW</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr">
+      <c r="E161" t="inlineStr">
         <is>
           <t>AM-C5 White</t>
         </is>
       </c>
-      <c r="F160" t="n">
+      <c r="F161" t="n">
         <v>393</v>
       </c>
-      <c r="G160" t="n">
-        <v>0</v>
-      </c>
-      <c r="H160" t="n">
-        <v>0</v>
-      </c>
-      <c r="I160" t="n">
-        <v>0</v>
-      </c>
-      <c r="J160" t="n">
+      <c r="G161" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0</v>
+      </c>
+      <c r="I161" t="n">
+        <v>0</v>
+      </c>
+      <c r="J161" t="n">
         <v>493</v>
       </c>
-      <c r="K160" t="n">
-        <v>0</v>
-      </c>
-      <c r="L160" t="n">
-        <v>0</v>
-      </c>
-      <c r="M160" t="n">
-        <v>0</v>
-      </c>
-      <c r="N160" t="n">
-        <v>0</v>
-      </c>
-      <c r="O160" t="n">
-        <v>0</v>
-      </c>
-      <c r="P160" t="n">
+      <c r="K161" t="n">
+        <v>0</v>
+      </c>
+      <c r="L161" t="n">
+        <v>0</v>
+      </c>
+      <c r="M161" t="n">
+        <v>0</v>
+      </c>
+      <c r="N161" t="n">
+        <v>0</v>
+      </c>
+      <c r="O161" t="n">
+        <v>0</v>
+      </c>
+      <c r="P161" t="n">
         <v>5</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
-      <c r="R160" t="n">
-        <v>0</v>
-      </c>
-      <c r="S160" t="n">
-        <v>0</v>
-      </c>
-      <c r="T160" t="n">
+      <c r="Q161" t="n">
+        <v>0</v>
+      </c>
+      <c r="R161" t="n">
+        <v>0</v>
+      </c>
+      <c r="S161" t="n">
+        <v>0</v>
+      </c>
+      <c r="T161" t="n">
         <v>10411.02</v>
       </c>
-      <c r="U160" t="n">
-        <v>0</v>
-      </c>
-      <c r="V160" t="n">
-        <v>0</v>
-      </c>
-      <c r="W160" t="n">
+      <c r="U161" t="n">
+        <v>0</v>
+      </c>
+      <c r="V161" t="n">
+        <v>0</v>
+      </c>
+      <c r="W161" t="n">
         <v>0</v>
       </c>
     </row>
